--- a/data/fmsForecastOutput/File1/RPT_RPT3325127211997VZ_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT3325127211997VZ_fmsForecastOutput.xlsx
@@ -1875,49 +1875,49 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>442.5127656309309</v>
+        <v>442.5224983623301</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>467.0539161019681</v>
+        <v>467.065761743038</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>497.885757728417</v>
+        <v>487.8853184875399</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>525.7099837566024</v>
+        <v>525.7264880047029</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>554.5901215023863</v>
+        <v>554.6091382059029</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>438.5914687043146</v>
+        <v>438.5914486188114</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>464.0499710971985</v>
+        <v>464.0499664693383</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>495.7543108239863</v>
+        <v>485.7830029124506</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>524.516142744865</v>
+        <v>524.5161689179656</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>554.4564960112424</v>
+        <v>554.4565449719358</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>49262485.89615832</v>
+        <v>49262487.66391281</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>56909334.46022814</v>
+        <v>56909339.23464894</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>65589520.7318522</v>
+        <v>64270298.72995762</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>74668629.94129071</v>
+        <v>74668642.2862041</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>86629392.59239623</v>
+        <v>86629411.13205823</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>542.7165981449876</v>
+        <v>542.7292129251797</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>572.8149156007918</v>
+        <v>572.830159355073</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>610.6284059713886</v>
+        <v>598.3641868614957</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>644.7532278271008</v>
+        <v>644.7742749908508</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>680.1730650130473</v>
+        <v>680.1972378207673</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>537.9638116605025</v>
+        <v>537.9645918051306</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>569.1741052760838</v>
+        <v>569.174975655359</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>608.0451375670337</v>
+        <v>595.8162174339215</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>643.3063523092549</v>
+        <v>643.3074244496721</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>680.0111215034034</v>
+        <v>680.0123063450523</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>49262485.89615832</v>
+        <v>49262487.66391281</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>56909334.46022814</v>
+        <v>56909339.23464894</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>65589520.7318522</v>
+        <v>64270298.72995762</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>74668629.94129071</v>
+        <v>74668642.2862041</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>86629392.59239623</v>
+        <v>86629411.13205823</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>851.368099959485</v>
+        <v>851.3680999594849</v>
       </c>
       <c r="D9" s="156" t="n">
         <v>889.1754653166771</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>938.8343571104809</v>
+        <v>928.3560617393657</v>
       </c>
       <c r="F9" s="156" t="n">
         <v>979.4055405063607</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>1021.313500162778</v>
+        <v>1021.313500162777</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>843.2473733544037</v>
+        <v>843.2473733544036</v>
       </c>
       <c r="I9" s="156" t="n">
         <v>882.6571928898776</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>933.9342427114581</v>
+        <v>923.5106373350542</v>
       </c>
       <c r="K9" s="156" t="n">
         <v>976.295665529395</v>
@@ -2058,13 +2058,13 @@
         <v>23032062.09360681</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>25906464.01794768</v>
+        <v>25617322.93576924</v>
       </c>
       <c r="P9" s="159" t="n">
         <v>28901815.03433856</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>32912312.71435727</v>
+        <v>32912312.71435726</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>861.2299125315155</v>
+        <v>861.2299125315153</v>
       </c>
       <c r="U9" s="156" t="n">
         <v>899.4752190695115</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>949.7093340639831</v>
+        <v>939.1096634792215</v>
       </c>
       <c r="W9" s="156" t="n">
         <v>990.7504732950588</v>
@@ -2087,13 +2087,13 @@
         <v>1033.143873319076</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>852.9490772297797</v>
+        <v>852.9490772297796</v>
       </c>
       <c r="Z9" s="156" t="n">
         <v>892.828312908976</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>944.7124335589612</v>
+        <v>934.1685331950432</v>
       </c>
       <c r="AB9" s="156" t="n">
         <v>987.5791200530349</v>
@@ -2108,13 +2108,13 @@
         <v>23032062.09360681</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>25906464.01794768</v>
+        <v>25617322.93576924</v>
       </c>
       <c r="AG9" s="159" t="n">
         <v>28901815.03433856</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>32912312.71435727</v>
+        <v>32912312.71435726</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>515.92485671264</v>
+        <v>515.9341644092066</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>541.0578579140042</v>
+        <v>541.0691695458598</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>574.253255978865</v>
+        <v>564.1718269397522</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>603.7564054388477</v>
+        <v>603.7720885075751</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>634.4096624700481</v>
+        <v>634.4276815522574</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>511.2902720635586</v>
+        <v>511.2902507153066</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>537.4926036767955</v>
+        <v>537.4925941764641</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>571.7014829126275</v>
+        <v>561.6517743986739</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>602.2913305069403</v>
+        <v>602.2913447422072</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>634.1653799219853</v>
+        <v>634.1654121983591</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>70004763.37038659</v>
+        <v>70004765.13814108</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>79941396.55383494</v>
+        <v>79941401.32825576</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>91495984.74979988</v>
+        <v>89887621.66572684</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>103570444.9756293</v>
+        <v>103570457.3205427</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>119541705.3067535</v>
+        <v>119541723.8464155</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>609.5073410707038</v>
+        <v>609.5185355655134</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>639.754256890122</v>
+        <v>639.7677886973948</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>679.3005711954513</v>
+        <v>667.3750766627687</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>714.3712349128458</v>
+        <v>714.3898531919323</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>750.7947662495176</v>
+        <v>750.8160980438734</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>604.0599394918383</v>
+        <v>604.0606297955234</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>635.5523431960946</v>
+        <v>635.5531113300067</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>676.2848280677914</v>
+        <v>664.3975280492934</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>712.6304847866071</v>
+        <v>712.6314241542688</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>750.4876810423575</v>
+        <v>750.4887148093875</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>70004763.37038659</v>
+        <v>70004765.13814108</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>79941396.55383494</v>
+        <v>79941401.32825576</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>91495984.74979988</v>
+        <v>89887621.66572684</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>103570444.9756293</v>
+        <v>103570457.3205427</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>119541705.3067535</v>
+        <v>119541723.8464155</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>839.569733226166</v>
+        <v>878.0970756141585</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>869.1720308384154</v>
+        <v>915.2596715726447</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>902.4776259888125</v>
+        <v>943.6036480853118</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>926.305302259115</v>
+        <v>984.9551176324392</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>947.9208742640598</v>
+        <v>1011.779076520688</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>835.8046916596272</v>
+        <v>836.2204483770092</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>866.8998500101986</v>
+        <v>867.2128392033861</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>901.7227626515989</v>
+        <v>891.1886318713506</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>926.305302259115</v>
+        <v>927.308849899995</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>947.9208742640598</v>
+        <v>950.5167657268634</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>7028916.928648425</v>
+        <v>7029034.309522301</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>7954622.429042895</v>
+        <v>7955408.972935619</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>9050687.642787918</v>
+        <v>8944220.771167107</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>10270977.88884246</v>
+        <v>10282873.56030074</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>11865024.34886792</v>
+        <v>11899950.43492213</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2368,49 +2368,49 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>1030.693919754367</v>
+        <v>1080.035426951667</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>1067.035044204461</v>
+        <v>1125.744405272297</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1107.922504836713</v>
+        <v>1160.606722463087</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>1137.174441968015</v>
+        <v>1211.467900922398</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>1163.710699476845</v>
+        <v>1244.460637938566</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>1025.686305468923</v>
+        <v>1024.333311866577</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>1064.012504341932</v>
+        <v>1061.861256529913</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>1106.918207818765</v>
+        <v>1090.933810037189</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>1137.174441968015</v>
+        <v>1134.860827361016</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>1163.710699476845</v>
+        <v>1163.062210496899</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>7028916.928648425</v>
+        <v>7029034.309522301</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>7954622.429042895</v>
+        <v>7955408.972935619</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>9050687.642787918</v>
+        <v>8944220.771167107</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>10270977.88884246</v>
+        <v>10282873.56030074</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>11865024.34886792</v>
+        <v>11899950.43492213</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>534.7334842439761</v>
+        <v>536.1099113800548</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>560.1964490353655</v>
+        <v>561.8597070294204</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>593.6892815859179</v>
+        <v>585.4777397481649</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>623.3393238961997</v>
+        <v>625.6401602151359</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>653.9381538014707</v>
+        <v>656.597997895243</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>530.0691431999252</v>
+        <v>530.0846686260809</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>556.634488427986</v>
+        <v>556.6479363342301</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>591.1775248317654</v>
+        <v>581.0977237826638</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>621.9183539240884</v>
+        <v>621.9805369018061</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>653.702030702886</v>
+        <v>653.8674759990962</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>77033680.29903501</v>
+        <v>77033799.44766338</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>87896018.98287784</v>
+        <v>87896810.30119136</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>100546672.3925878</v>
+        <v>98831842.43689395</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>113841422.8644717</v>
+        <v>113853330.8808434</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>131406729.6556214</v>
+        <v>131441674.2813376</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>633.1139980360379</v>
+        <v>634.750714798677</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>663.8105782197863</v>
+        <v>665.7811495944444</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>703.8100657689647</v>
+        <v>694.069109233347</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>739.166274438042</v>
+        <v>741.8825000835644</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>775.6450094449848</v>
+        <v>778.7841586582733</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>627.5997932131268</v>
+        <v>627.55456141225</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>659.5897709514311</v>
+        <v>659.5177989086026</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>700.8272263124742</v>
+        <v>688.7687107887598</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>737.4704909686477</v>
+        <v>737.4104312219964</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>775.3468456148613</v>
+        <v>775.3905262487328</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>77033680.29903501</v>
+        <v>77033799.44766338</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>87896018.98287784</v>
+        <v>87896810.30119136</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>100546672.3925878</v>
+        <v>98831842.43689395</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>113841422.8644717</v>
+        <v>113853330.8808434</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>131406729.6556214</v>
+        <v>131441674.2813376</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2606,10 +2606,10 @@
         <v>6249.235560822669</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>6361.676321627418</v>
+        <v>6364.450157963195</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>6650.85704119284</v>
+        <v>6650.857041192839</v>
       </c>
       <c r="F13" s="156" t="n">
         <v>6828.265131891069</v>
@@ -2621,10 +2621,10 @@
         <v>6246.754165223208</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>6359.39368784548</v>
+        <v>6362.166528900736</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>6648.671161826154</v>
+        <v>6648.671161826152</v>
       </c>
       <c r="K13" s="156" t="n">
         <v>6826.25819962299</v>
@@ -2636,10 +2636,10 @@
         <v>58276613.37108947</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>66475290.19997282</v>
+        <v>66504274.94645562</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>77352540.38490897</v>
+        <v>77352540.38490896</v>
       </c>
       <c r="P13" s="159" t="n">
         <v>89878921.09664796</v>
@@ -2656,7 +2656,7 @@
         <v>3793.881167961035</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>3862.143418723782</v>
+        <v>3863.827401562145</v>
       </c>
       <c r="V13" s="156" t="n">
         <v>4037.703657319148</v>
@@ -2671,10 +2671,10 @@
         <v>3792.846909154864</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>3861.192016308699</v>
+        <v>3862.875584313855</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>4036.792590784939</v>
+        <v>4036.792590784938</v>
       </c>
       <c r="AB13" s="156" t="n">
         <v>4144.570791947395</v>
@@ -2686,10 +2686,10 @@
         <v>58276613.37108947</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>66475290.19997282</v>
+        <v>66504274.94645562</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>77352540.38490897</v>
+        <v>77352540.38490896</v>
       </c>
       <c r="AG13" s="159" t="n">
         <v>89878921.09664796</v>
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>882.1591674302009</v>
+        <v>884.2909907513459</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>922.4377207128606</v>
+        <v>925.1756247288665</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>982.9253540965932</v>
+        <v>976.4373711717598</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>1040.481383505881</v>
+        <v>1044.022059920847</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>1101.009454223988</v>
+        <v>1105.065012530779</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>874.9073566573389</v>
+        <v>874.9309351884085</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>916.9160914036619</v>
+        <v>917.1059883869735</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>979.0124015109074</v>
+        <v>969.5796991461559</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>1038.248132685951</v>
+        <v>1038.304350371618</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>1100.619507603406</v>
+        <v>1100.768141957994</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>135310293.6701245</v>
+        <v>135310412.8187529</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>154371309.1828507</v>
+        <v>154401085.247647</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>177899212.7774968</v>
+        <v>176184382.8218029</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>203720343.9611197</v>
+        <v>203732251.9774913</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>237731663.5998514</v>
+        <v>237766608.2255676</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>987.4144795212828</v>
+        <v>989.6798500709419</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>1031.732975576244</v>
+        <v>1034.633787372027</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>1098.02075647907</v>
+        <v>1090.571310956767</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>1159.512347055807</v>
+        <v>1163.207104418583</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>1224.900565533283</v>
+        <v>1229.121169841711</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>979.7412679289688</v>
+        <v>979.6780280092395</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>1025.894246735829</v>
+        <v>1025.984792627453</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>1093.886312260865</v>
+        <v>1083.195107983967</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>1157.151063010141</v>
+        <v>1157.029945027695</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>1224.461595573067</v>
+        <v>1224.417577359301</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>135310293.6701245</v>
+        <v>135310412.8187529</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>154371309.1828507</v>
+        <v>154401085.247647</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>177899212.7774968</v>
+        <v>176184382.8218029</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>203720343.9611197</v>
+        <v>203732251.9774913</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>237731663.5998514</v>
+        <v>237766608.2255676</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3152,49 +3152,49 @@
         </is>
       </c>
       <c r="C19" s="74" t="n">
-        <v>111324.4401569304</v>
+        <v>111321.9957091933</v>
       </c>
       <c r="D19" s="75" t="n">
-        <v>121847.4623555101</v>
+        <v>121844.3823034031</v>
       </c>
       <c r="E19" s="75" t="n">
-        <v>131736.0854648698</v>
+        <v>131732.389343458</v>
       </c>
       <c r="F19" s="75" t="n">
-        <v>142033.88227046</v>
+        <v>142029.4468509568</v>
       </c>
       <c r="G19" s="76" t="n">
-        <v>156204.3556739109</v>
+        <v>156199.0330925568</v>
       </c>
       <c r="H19" s="74" t="n">
-        <v>995.3138995937665</v>
+        <v>997.7675215937664</v>
       </c>
       <c r="I19" s="75" t="n">
-        <v>788.7578896325715</v>
+        <v>791.8494533535065</v>
       </c>
       <c r="J19" s="75" t="n">
-        <v>566.3863438710613</v>
+        <v>570.0962203290647</v>
       </c>
       <c r="K19" s="75" t="n">
-        <v>323.2805625836594</v>
+        <v>327.732414344941</v>
       </c>
       <c r="L19" s="76" t="n">
-        <v>37.64566543256535</v>
+        <v>42.98788754186796</v>
       </c>
       <c r="M19" s="74" t="n">
-        <v>112319.7540565241</v>
+        <v>112319.7632307871</v>
       </c>
       <c r="N19" s="75" t="n">
-        <v>122636.2202451427</v>
+        <v>122636.2317567566</v>
       </c>
       <c r="O19" s="75" t="n">
-        <v>132302.4718087409</v>
+        <v>132302.485563787</v>
       </c>
       <c r="P19" s="75" t="n">
-        <v>142357.1628330436</v>
+        <v>142357.1792653017</v>
       </c>
       <c r="Q19" s="76" t="n">
-        <v>156242.0013393435</v>
+        <v>156242.0209800987</v>
       </c>
       <c r="S19" s="21" t="inlineStr">
         <is>
@@ -3202,49 +3202,49 @@
         </is>
       </c>
       <c r="T19" s="74" t="n">
-        <v>90770.18477882954</v>
+        <v>90768.07824366016</v>
       </c>
       <c r="U19" s="75" t="n">
-        <v>99350.30131074588</v>
+        <v>99347.66580502836</v>
       </c>
       <c r="V19" s="75" t="n">
-        <v>107413.1502734667</v>
+        <v>107410.0023717401</v>
       </c>
       <c r="W19" s="75" t="n">
-        <v>115809.6256344979</v>
+        <v>115805.8644434343</v>
       </c>
       <c r="X19" s="76" t="n">
-        <v>127363.7505635929</v>
+        <v>127359.2515747398</v>
       </c>
       <c r="Y19" s="74" t="n">
-        <v>801.9336952785828</v>
+        <v>803.9107205454717</v>
       </c>
       <c r="Z19" s="75" t="n">
-        <v>635.509590865103</v>
+        <v>638.0005871429162</v>
       </c>
       <c r="AA19" s="75" t="n">
-        <v>456.3427616968154</v>
+        <v>459.331911839464</v>
       </c>
       <c r="AB19" s="75" t="n">
-        <v>260.4701655128747</v>
+        <v>264.0571031429278</v>
       </c>
       <c r="AC19" s="76" t="n">
-        <v>30.33146387675285</v>
+        <v>34.63574720623246</v>
       </c>
       <c r="AD19" s="74" t="n">
-        <v>91572.11847410812</v>
+        <v>91571.98896420564</v>
       </c>
       <c r="AE19" s="75" t="n">
-        <v>99985.81090161098</v>
+        <v>99985.66639217128</v>
       </c>
       <c r="AF19" s="75" t="n">
-        <v>107869.4930351635</v>
+        <v>107869.3342835796</v>
       </c>
       <c r="AG19" s="75" t="n">
-        <v>116070.0958000108</v>
+        <v>116069.9215465772</v>
       </c>
       <c r="AH19" s="76" t="n">
-        <v>127394.0820274697</v>
+        <v>127393.8873219461</v>
       </c>
       <c r="AR19" s="77" t="inlineStr">
         <is>
@@ -3409,49 +3409,49 @@
         </is>
       </c>
       <c r="C21" s="85" t="n">
-        <v>135687.9058249714</v>
+        <v>135685.4613772344</v>
       </c>
       <c r="D21" s="86" t="n">
-        <v>147750.1812135974</v>
+        <v>147747.1011614904</v>
       </c>
       <c r="E21" s="86" t="n">
-        <v>159330.3717431031</v>
+        <v>159326.6756216912</v>
       </c>
       <c r="F21" s="86" t="n">
-        <v>171543.4305004977</v>
+        <v>171538.9950809944</v>
       </c>
       <c r="G21" s="87" t="n">
-        <v>188429.8307206147</v>
+        <v>188424.5081392605</v>
       </c>
       <c r="H21" s="85" t="n">
-        <v>1229.941424201886</v>
+        <v>1232.395046201886</v>
       </c>
       <c r="I21" s="86" t="n">
-        <v>980.0450387906911</v>
+        <v>983.1366025116262</v>
       </c>
       <c r="J21" s="86" t="n">
-        <v>711.1665150426037</v>
+        <v>714.8763915006072</v>
       </c>
       <c r="K21" s="86" t="n">
-        <v>417.2797565393044</v>
+        <v>421.7316083005861</v>
       </c>
       <c r="L21" s="87" t="n">
-        <v>72.58377804409656</v>
+        <v>77.92600015339917</v>
       </c>
       <c r="M21" s="85" t="n">
-        <v>136917.8472491733</v>
+        <v>136917.8564234363</v>
       </c>
       <c r="N21" s="86" t="n">
-        <v>148730.2262523881</v>
+        <v>148730.237764002</v>
       </c>
       <c r="O21" s="86" t="n">
-        <v>160041.5382581457</v>
+        <v>160041.5520131918</v>
       </c>
       <c r="P21" s="86" t="n">
-        <v>171960.710257037</v>
+        <v>171960.726689295</v>
       </c>
       <c r="Q21" s="87" t="n">
-        <v>188502.4144986588</v>
+        <v>188502.4341394139</v>
       </c>
       <c r="S21" s="42" t="inlineStr">
         <is>
@@ -3459,49 +3459,49 @@
         </is>
       </c>
       <c r="T21" s="85" t="n">
-        <v>114854.6681118086</v>
+        <v>114852.5615766392</v>
       </c>
       <c r="U21" s="86" t="n">
-        <v>124956.4120799042</v>
+        <v>124953.7765741866</v>
       </c>
       <c r="V21" s="86" t="n">
-        <v>134691.458581851</v>
+        <v>134688.3106801244</v>
       </c>
       <c r="W21" s="86" t="n">
-        <v>144981.2645217511</v>
+        <v>144977.5033306874</v>
       </c>
       <c r="X21" s="87" t="n">
-        <v>159220.2166031419</v>
+        <v>159215.7176142888</v>
       </c>
       <c r="Y21" s="85" t="n">
-        <v>1035.757313982224</v>
+        <v>1037.734339249113</v>
       </c>
       <c r="Z21" s="86" t="n">
-        <v>826.1413315458244</v>
+        <v>828.6323278236378</v>
       </c>
       <c r="AA21" s="86" t="n">
-        <v>600.6268715701337</v>
+        <v>603.6160217127822</v>
       </c>
       <c r="AB21" s="86" t="n">
-        <v>354.1472893824828</v>
+        <v>357.7342270125359</v>
       </c>
       <c r="AC21" s="87" t="n">
-        <v>65.14986779227041</v>
+        <v>69.45415112175002</v>
       </c>
       <c r="AD21" s="85" t="n">
-        <v>115890.4254257908</v>
+        <v>115890.2959158883</v>
       </c>
       <c r="AE21" s="86" t="n">
-        <v>125782.55341145</v>
+        <v>125782.4089020103</v>
       </c>
       <c r="AF21" s="86" t="n">
-        <v>135292.0854534212</v>
+        <v>135291.9267018372</v>
       </c>
       <c r="AG21" s="86" t="n">
-        <v>145335.4118111335</v>
+        <v>145335.2375576999</v>
       </c>
       <c r="AH21" s="87" t="n">
-        <v>159285.3664709342</v>
+        <v>159285.1717654105</v>
       </c>
       <c r="AR21" s="20" t="inlineStr">
         <is>
@@ -3566,49 +3566,49 @@
         </is>
       </c>
       <c r="C22" s="79" t="n">
-        <v>8372.046597771947</v>
+        <v>8004.848785774689</v>
       </c>
       <c r="D22" s="80" t="n">
-        <v>9151.95398242366</v>
+        <v>8691.969306662708</v>
       </c>
       <c r="E22" s="80" t="n">
-        <v>10028.71138536138</v>
+        <v>9478.789944608665</v>
       </c>
       <c r="F22" s="80" t="n">
-        <v>11088.11302687476</v>
+        <v>10439.94124830575</v>
       </c>
       <c r="G22" s="81" t="n">
-        <v>12516.89320385482</v>
+        <v>11761.41186457794</v>
       </c>
       <c r="H22" s="79" t="n">
-        <v>37.71347989806181</v>
+        <v>400.8704514966618</v>
       </c>
       <c r="I22" s="80" t="n">
-        <v>23.9876548361846</v>
+        <v>481.5675845154542</v>
       </c>
       <c r="J22" s="80" t="n">
-        <v>8.395381438574397</v>
+        <v>557.4924442114266</v>
       </c>
       <c r="K22" s="80" t="n">
-        <v>0</v>
+        <v>649.0002207740417</v>
       </c>
       <c r="L22" s="81" t="n">
-        <v>0</v>
+        <v>758.0416200980533</v>
       </c>
       <c r="M22" s="79" t="n">
-        <v>8409.760077670009</v>
+        <v>8405.719237271351</v>
       </c>
       <c r="N22" s="80" t="n">
-        <v>9175.941637259844</v>
+        <v>9173.536891178162</v>
       </c>
       <c r="O22" s="80" t="n">
-        <v>10037.10676679996</v>
+        <v>10036.28238882009</v>
       </c>
       <c r="P22" s="80" t="n">
-        <v>11088.11302687476</v>
+        <v>11088.94146907979</v>
       </c>
       <c r="Q22" s="81" t="n">
-        <v>12516.89320385482</v>
+        <v>12519.45348467599</v>
       </c>
       <c r="S22" s="32" t="inlineStr">
         <is>
@@ -3616,49 +3616,49 @@
         </is>
       </c>
       <c r="T22" s="79" t="n">
-        <v>6819.596772554498</v>
+        <v>6508.151616249585</v>
       </c>
       <c r="U22" s="80" t="n">
-        <v>7454.88395366953</v>
+        <v>7066.798587385697</v>
       </c>
       <c r="V22" s="80" t="n">
-        <v>8169.062008648177</v>
+        <v>7706.504363670506</v>
       </c>
       <c r="W22" s="80" t="n">
-        <v>9032.01611800852</v>
+        <v>8487.945534893228</v>
       </c>
       <c r="X22" s="81" t="n">
-        <v>10195.85396456519</v>
+        <v>9562.335739790255</v>
       </c>
       <c r="Y22" s="79" t="n">
-        <v>33.29469257523294</v>
+        <v>353.9061027498502</v>
       </c>
       <c r="Z22" s="80" t="n">
-        <v>21.17708563437581</v>
+        <v>425.149088465411</v>
       </c>
       <c r="AA22" s="80" t="n">
-        <v>7.411717104989739</v>
+        <v>492.1789009559794</v>
       </c>
       <c r="AB22" s="80" t="n">
-        <v>0</v>
+        <v>572.9659992658405</v>
       </c>
       <c r="AC22" s="81" t="n">
-        <v>0</v>
+        <v>669.2325525352885</v>
       </c>
       <c r="AD22" s="79" t="n">
-        <v>6852.891465129731</v>
+        <v>6862.057718999435</v>
       </c>
       <c r="AE22" s="80" t="n">
-        <v>7476.061039303906</v>
+        <v>7491.947675851108</v>
       </c>
       <c r="AF22" s="80" t="n">
-        <v>8176.473725753166</v>
+        <v>8198.683264626485</v>
       </c>
       <c r="AG22" s="80" t="n">
-        <v>9032.01611800852</v>
+        <v>9060.911534159068</v>
       </c>
       <c r="AH22" s="81" t="n">
-        <v>10195.85396456519</v>
+        <v>10231.56829232554</v>
       </c>
       <c r="AR22" s="88" t="inlineStr">
         <is>
@@ -3703,49 +3703,49 @@
         </is>
       </c>
       <c r="C23" s="85" t="n">
-        <v>144059.9524227434</v>
+        <v>143690.3101630091</v>
       </c>
       <c r="D23" s="86" t="n">
-        <v>156902.1351960211</v>
+        <v>156439.0704681531</v>
       </c>
       <c r="E23" s="86" t="n">
-        <v>169359.0831284644</v>
+        <v>168805.4655662999</v>
       </c>
       <c r="F23" s="86" t="n">
-        <v>182631.5435273724</v>
+        <v>181978.9363293002</v>
       </c>
       <c r="G23" s="87" t="n">
-        <v>200946.7239244695</v>
+        <v>200185.9200038385</v>
       </c>
       <c r="H23" s="85" t="n">
-        <v>1267.654904099948</v>
+        <v>1633.265497698548</v>
       </c>
       <c r="I23" s="86" t="n">
-        <v>1004.032693626876</v>
+        <v>1464.70418702708</v>
       </c>
       <c r="J23" s="86" t="n">
-        <v>719.5618964811781</v>
+        <v>1272.368835712034</v>
       </c>
       <c r="K23" s="86" t="n">
-        <v>417.2797565393044</v>
+        <v>1070.731829074628</v>
       </c>
       <c r="L23" s="87" t="n">
-        <v>72.58377804409656</v>
+        <v>835.9676202514524</v>
       </c>
       <c r="M23" s="85" t="n">
-        <v>145327.6073268433</v>
+        <v>145323.5756607076</v>
       </c>
       <c r="N23" s="86" t="n">
-        <v>157906.1678896479</v>
+        <v>157903.7746551802</v>
       </c>
       <c r="O23" s="86" t="n">
-        <v>170078.6450249456</v>
+        <v>170077.8344020119</v>
       </c>
       <c r="P23" s="86" t="n">
-        <v>183048.8232839117</v>
+        <v>183049.6681583748</v>
       </c>
       <c r="Q23" s="87" t="n">
-        <v>201019.3077025136</v>
+        <v>201021.8876240899</v>
       </c>
       <c r="S23" s="42" t="inlineStr">
         <is>
@@ -3753,49 +3753,49 @@
         </is>
       </c>
       <c r="T23" s="85" t="n">
-        <v>121674.2648843631</v>
+        <v>121360.7131928888</v>
       </c>
       <c r="U23" s="86" t="n">
-        <v>132411.2960335737</v>
+        <v>132020.5751615723</v>
       </c>
       <c r="V23" s="86" t="n">
-        <v>142860.5205904992</v>
+        <v>142394.815043795</v>
       </c>
       <c r="W23" s="86" t="n">
-        <v>154013.2806397596</v>
+        <v>153465.4488655806</v>
       </c>
       <c r="X23" s="87" t="n">
-        <v>169416.0705677071</v>
+        <v>168778.053354079</v>
       </c>
       <c r="Y23" s="85" t="n">
-        <v>1069.052006557457</v>
+        <v>1391.640441998963</v>
       </c>
       <c r="Z23" s="86" t="n">
-        <v>847.3184171802002</v>
+        <v>1253.781416289049</v>
       </c>
       <c r="AA23" s="86" t="n">
-        <v>608.0385886751235</v>
+        <v>1095.794922668762</v>
       </c>
       <c r="AB23" s="86" t="n">
-        <v>354.1472893824828</v>
+        <v>930.7002262783765</v>
       </c>
       <c r="AC23" s="87" t="n">
-        <v>65.14986779227041</v>
+        <v>738.6867036570386</v>
       </c>
       <c r="AD23" s="85" t="n">
-        <v>122743.3168909205</v>
+        <v>122752.3536348877</v>
       </c>
       <c r="AE23" s="86" t="n">
-        <v>133258.6144507539</v>
+        <v>133274.3565778614</v>
       </c>
       <c r="AF23" s="86" t="n">
-        <v>143468.5591791743</v>
+        <v>143490.6099664637</v>
       </c>
       <c r="AG23" s="86" t="n">
-        <v>154367.4279291421</v>
+        <v>154396.149091859</v>
       </c>
       <c r="AH23" s="87" t="n">
-        <v>169481.2204354994</v>
+        <v>169516.7400577361</v>
       </c>
       <c r="AR23" s="90" t="inlineStr">
         <is>
@@ -3942,49 +3942,49 @@
         </is>
       </c>
       <c r="C25" s="91" t="n">
-        <v>153385.3511541392</v>
+        <v>153015.7088944049</v>
       </c>
       <c r="D25" s="92" t="n">
-        <v>167351.4706917584</v>
+        <v>166888.4059638904</v>
       </c>
       <c r="E25" s="92" t="n">
-        <v>180989.5451735538</v>
+        <v>180435.9276113893</v>
       </c>
       <c r="F25" s="92" t="n">
-        <v>195794.3190436412</v>
+        <v>195141.711845569</v>
       </c>
       <c r="G25" s="93" t="n">
-        <v>215921.5460755595</v>
+        <v>215160.7421549284</v>
       </c>
       <c r="H25" s="91" t="n">
-        <v>1271.359228419948</v>
+        <v>1636.969822018548</v>
       </c>
       <c r="I25" s="92" t="n">
-        <v>1007.783366626876</v>
+        <v>1468.45486002708</v>
       </c>
       <c r="J25" s="92" t="n">
-        <v>723.3856360511782</v>
+        <v>1276.192575282034</v>
       </c>
       <c r="K25" s="92" t="n">
-        <v>421.1496363693044</v>
+        <v>1074.601708904628</v>
       </c>
       <c r="L25" s="93" t="n">
-        <v>76.50044054409656</v>
+        <v>839.8842827514525</v>
       </c>
       <c r="M25" s="91" t="n">
-        <v>154656.7103825592</v>
+        <v>154652.6787164235</v>
       </c>
       <c r="N25" s="92" t="n">
-        <v>168359.2540583852</v>
+        <v>168356.8608239175</v>
       </c>
       <c r="O25" s="92" t="n">
-        <v>181712.930809605</v>
+        <v>181712.1201866713</v>
       </c>
       <c r="P25" s="92" t="n">
-        <v>196215.4686800106</v>
+        <v>196216.3135544736</v>
       </c>
       <c r="Q25" s="93" t="n">
-        <v>215998.0465161036</v>
+        <v>216000.6264376799</v>
       </c>
       <c r="S25" s="51" t="inlineStr">
         <is>
@@ -3992,49 +3992,49 @@
         </is>
       </c>
       <c r="T25" s="91" t="n">
-        <v>137034.9498376056</v>
+        <v>136721.3981461314</v>
       </c>
       <c r="U25" s="92" t="n">
-        <v>149623.3161459545</v>
+        <v>149232.5952739531</v>
       </c>
       <c r="V25" s="92" t="n">
-        <v>162018.0781900254</v>
+        <v>161552.3726433211</v>
       </c>
       <c r="W25" s="92" t="n">
-        <v>175694.8466123705</v>
+        <v>175147.0148381915</v>
       </c>
       <c r="X25" s="93" t="n">
-        <v>194082.4180257854</v>
+        <v>193444.4008121573</v>
       </c>
       <c r="Y25" s="91" t="n">
-        <v>1073.240660637687</v>
+        <v>1395.829096079193</v>
       </c>
       <c r="Z25" s="92" t="n">
-        <v>851.5594798971542</v>
+        <v>1258.022479006003</v>
       </c>
       <c r="AA25" s="92" t="n">
-        <v>612.3622712061436</v>
+        <v>1100.118605199782</v>
       </c>
       <c r="AB25" s="92" t="n">
-        <v>358.5231448799109</v>
+        <v>935.0760817758046</v>
       </c>
       <c r="AC25" s="93" t="n">
-        <v>69.57862265936811</v>
+        <v>743.1154585241363</v>
       </c>
       <c r="AD25" s="91" t="n">
-        <v>138108.1904982433</v>
+        <v>138117.2272422106</v>
       </c>
       <c r="AE25" s="92" t="n">
-        <v>150474.8756258516</v>
+        <v>150490.6177529591</v>
       </c>
       <c r="AF25" s="92" t="n">
-        <v>162630.4404612315</v>
+        <v>162652.4912485209</v>
       </c>
       <c r="AG25" s="92" t="n">
-        <v>176053.3697572504</v>
+        <v>176082.0909199673</v>
       </c>
       <c r="AH25" s="93" t="n">
-        <v>194151.9966484447</v>
+        <v>194187.5162706814</v>
       </c>
     </row>
     <row r="28" ht="1.95" customHeight="1">
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>454.9781866303243</v>
+        <v>454.9882004603118</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>491.5070694451437</v>
+        <v>491.5195352785887</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>527.2984719396595</v>
+        <v>516.7029452702044</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>563.8309448169133</v>
+        <v>563.8486458423598</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>596.3012348905719</v>
+        <v>596.321681853745</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>450.9464282190903</v>
+        <v>450.9464144373578</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>488.3458493907414</v>
+        <v>488.3458445205841</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>525.0411093252826</v>
+        <v>514.476453493605</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>562.5505344644237</v>
+        <v>562.5505625354219</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>596.1575593321863</v>
+        <v>596.1576119752481</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>50650191.91023623</v>
+        <v>50650194.49937641</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>59888889.14168423</v>
+        <v>59888894.16607541</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>69464236.56493823</v>
+        <v>68066513.56124604</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>80083098.03656769</v>
+        <v>80083111.27665138</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>93144850.1836392</v>
+        <v>93144870.11768223</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,49 +4458,49 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>558.0047240583501</v>
+        <v>558.0177026928975</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>602.8053096121466</v>
+        <v>602.8213514709895</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>646.7014177322509</v>
+        <v>633.7074020878573</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>691.5064062922947</v>
+        <v>691.5289796551556</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>731.3293599746171</v>
+        <v>731.3553508362199</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>553.1180533358252</v>
+        <v>553.118863882873</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>598.9738804100582</v>
+        <v>598.9747963590571</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>643.96554216023</v>
+        <v>631.0089332924293</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>689.9546130689092</v>
+        <v>689.9557629537568</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>731.1552365796285</v>
+        <v>731.1565105340517</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>50650191.91023623</v>
+        <v>50650194.49937641</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>59888889.14168423</v>
+        <v>59888894.16607541</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>69464236.56493823</v>
+        <v>68066513.56124604</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>80083098.03656769</v>
+        <v>80083111.27665138</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>93144850.1836392</v>
+        <v>93144870.11768223</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4510,28 +4510,28 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>875.6653356440744</v>
+        <v>875.6653356440743</v>
       </c>
       <c r="D36" s="156" t="n">
         <v>936.067405281334</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>994.6655828011827</v>
+        <v>983.5638629669625</v>
       </c>
       <c r="F36" s="156" t="n">
         <v>1050.816358260223</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>1098.550016726195</v>
+        <v>1098.550016726194</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>867.3128512267576</v>
+        <v>867.3128512267575</v>
       </c>
       <c r="I36" s="156" t="n">
         <v>929.205382434923</v>
       </c>
       <c r="J36" s="156" t="n">
-        <v>989.4740651414568</v>
+        <v>978.4302891785931</v>
       </c>
       <c r="K36" s="156" t="n">
         <v>1047.479734805703</v>
@@ -4546,13 +4546,13 @@
         <v>24246690.83122163</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>27447086.84292156</v>
+        <v>27140742.80763534</v>
       </c>
       <c r="P36" s="159" t="n">
         <v>31009116.00499258</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>35401296.15156598</v>
+        <v>35401296.15156597</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4560,28 +4560,28 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>885.8085949655795</v>
+        <v>885.8085949655792</v>
       </c>
       <c r="U36" s="156" t="n">
         <v>946.9103312802183</v>
       </c>
       <c r="V36" s="156" t="n">
-        <v>1006.187280113898</v>
+        <v>994.9569636359494</v>
       </c>
       <c r="W36" s="156" t="n">
         <v>1062.988477433209</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>1111.275058181789</v>
+        <v>1111.275058181788</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>877.2914325017135</v>
+        <v>877.2914325017134</v>
       </c>
       <c r="Z36" s="156" t="n">
         <v>939.9128910161362</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>1000.893220607677</v>
+        <v>989.721992497156</v>
       </c>
       <c r="AB36" s="156" t="n">
         <v>1059.585893185199</v>
@@ -4596,13 +4596,13 @@
         <v>24246690.83122163</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>27447086.84292156</v>
+        <v>27140742.80763534</v>
       </c>
       <c r="AG36" s="159" t="n">
         <v>31009116.00499258</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>35401296.15156598</v>
+        <v>35401296.15156597</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,49 +4612,49 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>530.514741267726</v>
+        <v>530.5243178626372</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>569.4448513147603</v>
+        <v>569.4567564160548</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>608.2413688465821</v>
+        <v>597.5600507409291</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>647.6040132661213</v>
+        <v>647.6208353044756</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>682.1963690335253</v>
+        <v>682.2157453861707</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>525.7490947903354</v>
+        <v>525.7490784723743</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>565.6925434251126</v>
+        <v>565.6925334228224</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>605.5385649414507</v>
+        <v>594.8908591003521</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>646.0325377553164</v>
+        <v>646.0325530164191</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>681.9336859800266</v>
+        <v>681.9337206763979</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>71984434.2518943</v>
+        <v>71984436.84103447</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>84135579.97290586</v>
+        <v>84135584.99729703</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>96911323.40785979</v>
+        <v>95207256.36888137</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>111092214.0415603</v>
+        <v>111092227.281644</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>128546146.3352052</v>
+        <v>128546166.2692482</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,49 +4662,49 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>626.7436529599214</v>
+        <v>626.755170741233</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>673.3194285308451</v>
+        <v>673.3336702900266</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>719.5060802535409</v>
+        <v>706.8709666645988</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>766.2522078836846</v>
+        <v>766.2721782996041</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>807.3481438328137</v>
+        <v>807.3710824245397</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>621.1422038310557</v>
+        <v>621.1429203121533</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>668.8970583836709</v>
+        <v>668.8978668141278</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>716.3118454643436</v>
+        <v>703.7172039001533</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>764.3850363593903</v>
+        <v>764.3860439388551</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>807.017927529845</v>
+        <v>807.0190391517822</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>71984434.2518943</v>
+        <v>71984436.84103447</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>84135579.97290586</v>
+        <v>84135584.99729703</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>96911323.40785979</v>
+        <v>95207256.36888137</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>111092214.0415603</v>
+        <v>111092227.281644</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>128546146.3352052</v>
+        <v>128546166.2692482</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4714,49 +4714,49 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>863.3906662027555</v>
+        <v>903.0111254164957</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>914.8649995349315</v>
+        <v>963.3754861969015</v>
       </c>
       <c r="E38" s="156" t="n">
-        <v>955.9974705078605</v>
+        <v>999.5601346616606</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>993.6907271849807</v>
+        <v>1056.607099354782</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>1019.45152175397</v>
+        <v>1088.128492702548</v>
       </c>
       <c r="H38" s="155" t="n">
-        <v>859.5187999148609</v>
+        <v>859.9463421023996</v>
       </c>
       <c r="I38" s="156" t="n">
-        <v>912.47336860504</v>
+        <v>912.8027996341661</v>
       </c>
       <c r="J38" s="156" t="n">
-        <v>955.1978413312761</v>
+        <v>944.0368640899222</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>993.6907271849807</v>
+        <v>994.7672706691702</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>1019.45152175397</v>
+        <v>1022.243293600788</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>7228346.889530834</v>
+        <v>7228467.51083127</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>8372802.375873736</v>
+        <v>8373630.156814732</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>9587422.716858864</v>
+        <v>9474620.553462632</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>11018155.09678444</v>
+        <v>11030916.03980668</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>12760365.82430171</v>
+        <v>12797927.36425705</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4764,49 +4764,49 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>1059.937578512172</v>
+        <v>1110.679027941389</v>
       </c>
       <c r="U38" s="156" t="n">
-        <v>1123.129806970688</v>
+        <v>1184.925543479015</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>1173.625895691468</v>
+        <v>1229.431673084786</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1219.899848807383</v>
+        <v>1299.59788201509</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1251.524969722915</v>
+        <v>1338.368335155085</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>1054.787884254635</v>
+        <v>1053.39648933837</v>
       </c>
       <c r="Z38" s="156" t="n">
-        <v>1119.948370118354</v>
+        <v>1117.684014773029</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>1172.562040609472</v>
+        <v>1155.627098602678</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>1219.899848807383</v>
+        <v>1217.417916312373</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>1251.524969722915</v>
+        <v>1250.827536757632</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>7228346.889530834</v>
+        <v>7228467.51083127</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>8372802.375873736</v>
+        <v>8373630.156814732</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>9587422.716858864</v>
+        <v>9474620.553462632</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>11018155.09678444</v>
+        <v>11030916.03980668</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>12760365.82430171</v>
+        <v>12797927.36425705</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4816,49 +4816,49 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>549.8598313358838</v>
+        <v>551.27519915576</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>589.5928836991732</v>
+        <v>591.3434212902985</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>628.8339790074078</v>
+        <v>620.1332200421509</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>668.6159837445773</v>
+        <v>671.0839495207432</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>703.2038612016397</v>
+        <v>706.0641109564301</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>545.063547102064</v>
+        <v>545.0795164633651</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>585.8440084077571</v>
+        <v>585.8581617578633</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>626.1735334797521</v>
+        <v>615.4939430549668</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>667.0918006883307</v>
+        <v>667.158507033127</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>702.9499493084761</v>
+        <v>703.1278797750527</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>79212781.14142513</v>
+        <v>79212904.35186575</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>92508382.34877959</v>
+        <v>92509215.15411176</v>
       </c>
       <c r="O39" s="165" t="n">
-        <v>106498746.1247187</v>
+        <v>104681876.922344</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>122110369.1383447</v>
+        <v>122123143.3214506</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>141306512.1595069</v>
+        <v>141344093.6335053</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,49 +4866,49 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>651.0232974631691</v>
+        <v>652.7063187735724</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>698.6441876176752</v>
+        <v>700.718164883732</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>745.4735967957913</v>
+        <v>735.1523079695567</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>792.856100662926</v>
+        <v>795.7696290871145</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>834.0797404047554</v>
+        <v>837.4554085949779</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>645.3531088117809</v>
+        <v>645.306603142414</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>694.2018925385595</v>
+        <v>694.1261434645618</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>742.3141818251273</v>
+        <v>729.5381694092039</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>791.0371428511199</v>
+        <v>790.9727285283046</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>833.7591138204298</v>
+        <v>833.8061101538677</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>79212781.14142513</v>
+        <v>79212904.35186575</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>92508382.34877959</v>
+        <v>92509215.15411176</v>
       </c>
       <c r="AF39" s="165" t="n">
-        <v>106498746.1247187</v>
+        <v>104681876.922344</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>122110369.1383447</v>
+        <v>122123143.3214506</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>141306512.1595069</v>
+        <v>141344093.6335053</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4921,10 +4921,10 @@
         <v>6427.932072436402</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>6697.206360277312</v>
+        <v>6700.126495381824</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>7046.892393719899</v>
+        <v>7046.892393719898</v>
       </c>
       <c r="F40" s="156" t="n">
         <v>7326.464733788702</v>
@@ -4936,10 +4936,10 @@
         <v>6425.379721480363</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>6694.803334925235</v>
+        <v>6697.722422255749</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>7044.576352856701</v>
+        <v>7044.576352856699</v>
       </c>
       <c r="K40" s="156" t="n">
         <v>7324.311372986042</v>
@@ -4951,10 +4951,10 @@
         <v>59943029.59379703</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>69981356.14272326</v>
+        <v>70011869.6141232</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>81958614.52098854</v>
+        <v>81958614.52098852</v>
       </c>
       <c r="P40" s="159" t="n">
         <v>96436610.61872099</v>
@@ -4971,7 +4971,7 @@
         <v>3902.36696971923</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>4065.842108352229</v>
+        <v>4067.614908476834</v>
       </c>
       <c r="V40" s="156" t="n">
         <v>4278.134835048896</v>
@@ -4986,10 +4986,10 @@
         <v>3901.303136345262</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>4064.840526696178</v>
+        <v>4066.61289010828</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>4277.169517678469</v>
+        <v>4277.169517678468</v>
       </c>
       <c r="AB40" s="156" t="n">
         <v>4446.96436904227</v>
@@ -5001,10 +5001,10 @@
         <v>59943029.59379703</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>69981356.14272326</v>
+        <v>70011869.6141232</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>81958614.52098854</v>
+        <v>81958614.52098852</v>
       </c>
       <c r="AG40" s="159" t="n">
         <v>96436610.61872099</v>
@@ -5020,49 +5020,49 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>907.2301213130999</v>
+        <v>909.4225354449936</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>970.9489723624225</v>
+        <v>973.8308891475638</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>1041.261032315388</v>
+        <v>1034.386521099646</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>1116.206950357702</v>
+        <v>1120.005312411809</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>1184.093457238351</v>
+        <v>1188.455054104303</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>899.7722141574462</v>
+        <v>899.7964671586707</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>965.1369590598989</v>
+        <v>965.3368682029175</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>1037.115849741969</v>
+        <v>1027.121863151442</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>1113.811164977383</v>
+        <v>1113.871471647514</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>1183.674084597787</v>
+        <v>1183.833934540158</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>139155810.7352222</v>
+        <v>139155933.9456628</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>162489738.4915029</v>
+        <v>162521084.768235</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>188457360.6457072</v>
+        <v>186640491.4433325</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>218546979.7570657</v>
+        <v>218559753.9401716</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>255671289.9848592</v>
+        <v>255708871.4588575</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,49 +5070,49 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>1015.476788221763</v>
+        <v>1017.806545519153</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>1085.99209452755</v>
+        <v>1089.045489491673</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>1163.187236579069</v>
+        <v>1155.294028738293</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>1243.900910988234</v>
+        <v>1247.864567615307</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>1317.333597682667</v>
+        <v>1321.872695127329</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>1007.585504039981</v>
+        <v>1007.520471733991</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>1079.846305342864</v>
+        <v>1079.941641511664</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>1158.80741705691</v>
+        <v>1147.480066309957</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>1241.367774206238</v>
+        <v>1241.237838546063</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>1316.861502319797</v>
+        <v>1316.814161742614</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>139155810.7352222</v>
+        <v>139155933.9456628</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>162489738.4915029</v>
+        <v>162521084.768235</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>188457360.6457072</v>
+        <v>186640491.4433325</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>218546979.7570657</v>
+        <v>218559753.9401716</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>255671289.9848592</v>
+        <v>255708871.4588575</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -5371,49 +5371,49 @@
         </is>
       </c>
       <c r="C46" s="148" t="n">
-        <v>0.1644121889215586</v>
+        <v>0.1644158075471457</v>
       </c>
       <c r="D46" s="149" t="n">
-        <v>0.1773526030604322</v>
+        <v>0.1773571011605577</v>
       </c>
       <c r="E46" s="149" t="n">
-        <v>0.1944331849918608</v>
+        <v>0.1944386638589151</v>
       </c>
       <c r="F46" s="149" t="n">
-        <v>0.2142553568951812</v>
+        <v>0.2142620832722261</v>
       </c>
       <c r="G46" s="150" t="n">
-        <v>0.2323794694415245</v>
+        <v>0.2323874376531865</v>
       </c>
       <c r="H46" s="148" t="n">
-        <v>0.1629552614356427</v>
+        <v>0.1629552564554373</v>
       </c>
       <c r="I46" s="149" t="n">
-        <v>0.1762119264753975</v>
+        <v>0.1762119247180778</v>
       </c>
       <c r="J46" s="149" t="n">
-        <v>0.1936008173174764</v>
+        <v>0.1936008205872681</v>
       </c>
       <c r="K46" s="149" t="n">
-        <v>0.2137688018744488</v>
+        <v>0.2137688125414081</v>
       </c>
       <c r="L46" s="150" t="n">
-        <v>0.232323478864823</v>
+        <v>0.2323234993799017</v>
       </c>
       <c r="M46" s="151" t="n">
-        <v>18303.09488666798</v>
+        <v>18303.09582228691</v>
       </c>
       <c r="N46" s="152" t="n">
-        <v>21609.96462505774</v>
+        <v>21609.96643803034</v>
       </c>
       <c r="O46" s="152" t="n">
-        <v>25613.86667529462</v>
+        <v>25613.86977088436</v>
       </c>
       <c r="P46" s="152" t="n">
-        <v>30431.52013706555</v>
+        <v>30431.52516828791</v>
       </c>
       <c r="Q46" s="153" t="n">
-        <v>36298.68529595861</v>
+        <v>36298.69306428455</v>
       </c>
       <c r="S46" s="21" t="inlineStr">
         <is>
@@ -5421,49 +5421,49 @@
         </is>
       </c>
       <c r="T46" s="148" t="n">
-        <v>0.2016421463861207</v>
+        <v>0.2016468363817686</v>
       </c>
       <c r="U46" s="149" t="n">
-        <v>0.2175128242184844</v>
+        <v>0.2175186126711855</v>
       </c>
       <c r="V46" s="149" t="n">
-        <v>0.238461181057286</v>
+        <v>0.238468198541102</v>
       </c>
       <c r="W46" s="149" t="n">
-        <v>0.2627719411951925</v>
+        <v>0.2627805190569798</v>
       </c>
       <c r="X46" s="150" t="n">
-        <v>0.2850001286499066</v>
+        <v>0.2850102573269515</v>
       </c>
       <c r="Y46" s="148" t="n">
-        <v>0.1998762853984114</v>
+        <v>0.1998765782999577</v>
       </c>
       <c r="Z46" s="149" t="n">
-        <v>0.2161303131933648</v>
+        <v>0.2161306436991689</v>
       </c>
       <c r="AA46" s="149" t="n">
-        <v>0.2374523691044413</v>
+        <v>0.2374527472613079</v>
       </c>
       <c r="AB46" s="149" t="n">
-        <v>0.2621822608770752</v>
+        <v>0.2621826978324971</v>
       </c>
       <c r="AC46" s="150" t="n">
-        <v>0.2849322725064388</v>
+        <v>0.2849327689683538</v>
       </c>
       <c r="AD46" s="151" t="n">
-        <v>18303.09488666798</v>
+        <v>18303.09582228691</v>
       </c>
       <c r="AE46" s="152" t="n">
-        <v>21609.96462505774</v>
+        <v>21609.96643803034</v>
       </c>
       <c r="AF46" s="152" t="n">
-        <v>25613.86667529462</v>
+        <v>25613.86977088436</v>
       </c>
       <c r="AG46" s="152" t="n">
-        <v>30431.52013706555</v>
+        <v>30431.52516828791</v>
       </c>
       <c r="AH46" s="153" t="n">
-        <v>36298.68529595861</v>
+        <v>36298.69306428455</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" thickBot="1">
@@ -5575,49 +5575,49 @@
         </is>
       </c>
       <c r="C48" s="161" t="n">
-        <v>0.1398754629063015</v>
+        <v>0.1398779897347047</v>
       </c>
       <c r="D48" s="162" t="n">
-        <v>0.151001031530668</v>
+        <v>0.151004191687546</v>
       </c>
       <c r="E48" s="162" t="n">
-        <v>0.1653251260648476</v>
+        <v>0.1653289807698159</v>
       </c>
       <c r="F48" s="162" t="n">
-        <v>0.181809409367104</v>
+        <v>0.1818141396747646</v>
       </c>
       <c r="G48" s="163" t="n">
-        <v>0.1968148579029957</v>
+        <v>0.1968204587212187</v>
       </c>
       <c r="H48" s="161" t="n">
-        <v>0.138618953039149</v>
+        <v>0.1386189505843356</v>
       </c>
       <c r="I48" s="162" t="n">
-        <v>0.1500060232157289</v>
+        <v>0.1500060237950407</v>
       </c>
       <c r="J48" s="162" t="n">
-        <v>0.1645904812030688</v>
+        <v>0.1645904863994698</v>
       </c>
       <c r="K48" s="162" t="n">
-        <v>0.1813682307632016</v>
+        <v>0.1813682426899527</v>
       </c>
       <c r="L48" s="163" t="n">
-        <v>0.196739073377902</v>
+        <v>0.1967390940896874</v>
       </c>
       <c r="M48" s="164" t="n">
-        <v>18979.40863805453</v>
+        <v>18979.40957367346</v>
       </c>
       <c r="N48" s="165" t="n">
-        <v>22310.42977209634</v>
+        <v>22310.43158506894</v>
       </c>
       <c r="O48" s="165" t="n">
-        <v>26341.31379438754</v>
+        <v>26341.31688997729</v>
       </c>
       <c r="P48" s="165" t="n">
-        <v>31188.20978010233</v>
+        <v>31188.21481132469</v>
       </c>
       <c r="Q48" s="166" t="n">
-        <v>37085.79035796332</v>
+        <v>37085.79812628926</v>
       </c>
       <c r="S48" s="42" t="inlineStr">
         <is>
@@ -5625,49 +5625,49 @@
         </is>
       </c>
       <c r="T48" s="161" t="n">
-        <v>0.1652471680086915</v>
+        <v>0.1652502069882771</v>
       </c>
       <c r="U48" s="162" t="n">
-        <v>0.1785456976615957</v>
+        <v>0.178549478028965</v>
       </c>
       <c r="V48" s="162" t="n">
-        <v>0.1955678115875485</v>
+        <v>0.1955724053332001</v>
       </c>
       <c r="W48" s="162" t="n">
-        <v>0.215118897486394</v>
+        <v>0.2151245130783203</v>
       </c>
       <c r="X48" s="163" t="n">
-        <v>0.2329213660750132</v>
+        <v>0.2329279965696113</v>
       </c>
       <c r="Y48" s="161" t="n">
-        <v>0.1637702904991732</v>
+        <v>0.1637704815893168</v>
       </c>
       <c r="Z48" s="162" t="n">
-        <v>0.1773730073606967</v>
+        <v>0.1773732255553294</v>
       </c>
       <c r="AA48" s="162" t="n">
-        <v>0.1946995916731317</v>
+        <v>0.1946998430145025</v>
       </c>
       <c r="AB48" s="162" t="n">
-        <v>0.21459470470027</v>
+        <v>0.2145949966121779</v>
       </c>
       <c r="AC48" s="163" t="n">
-        <v>0.2328260980881166</v>
+        <v>0.2328264314578377</v>
       </c>
       <c r="AD48" s="164" t="n">
-        <v>18979.40863805453</v>
+        <v>18979.40957367346</v>
       </c>
       <c r="AE48" s="165" t="n">
-        <v>22310.42977209634</v>
+        <v>22310.43158506894</v>
       </c>
       <c r="AF48" s="165" t="n">
-        <v>26341.31379438754</v>
+        <v>26341.31688997729</v>
       </c>
       <c r="AG48" s="165" t="n">
-        <v>31188.20978010233</v>
+        <v>31188.21481132469</v>
       </c>
       <c r="AH48" s="166" t="n">
-        <v>37085.79035796332</v>
+        <v>37085.79812628926</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" thickBot="1">
@@ -5677,49 +5677,49 @@
         </is>
       </c>
       <c r="C49" s="155" t="n">
-        <v>0.1583253355720494</v>
+        <v>0.1656054334039842</v>
       </c>
       <c r="D49" s="156" t="n">
-        <v>0.1578648378075564</v>
+        <v>0.1662480726234891</v>
       </c>
       <c r="E49" s="156" t="n">
-        <v>0.1581866011023667</v>
+        <v>0.1674055676960299</v>
       </c>
       <c r="F49" s="156" t="n">
-        <v>0.1579475743243469</v>
+        <v>0.167957409001258</v>
       </c>
       <c r="G49" s="157" t="n">
-        <v>0.1553308581827811</v>
+        <v>0.1658026908268735</v>
       </c>
       <c r="H49" s="155" t="n">
-        <v>0.1576153272834295</v>
+        <v>0.1577076767712626</v>
       </c>
       <c r="I49" s="156" t="n">
-        <v>0.1574521491277678</v>
+        <v>0.1575208299347249</v>
       </c>
       <c r="J49" s="156" t="n">
-        <v>0.1580542883866029</v>
+        <v>0.158106572760074</v>
       </c>
       <c r="K49" s="156" t="n">
-        <v>0.1579475743243469</v>
+        <v>0.1581273999037802</v>
       </c>
       <c r="L49" s="157" t="n">
-        <v>0.1553308581827811</v>
+        <v>0.1557634873963994</v>
       </c>
       <c r="M49" s="158" t="n">
-        <v>1325.507087017078</v>
+        <v>1325.646452501574</v>
       </c>
       <c r="N49" s="159" t="n">
-        <v>1444.771731057531</v>
+        <v>1445.0231445352</v>
       </c>
       <c r="O49" s="159" t="n">
-        <v>1586.407767486924</v>
+        <v>1586.802211748633</v>
       </c>
       <c r="P49" s="159" t="n">
-        <v>1751.340556429061</v>
+        <v>1753.465482190792</v>
       </c>
       <c r="Q49" s="160" t="n">
-        <v>1944.259763136989</v>
+        <v>1950.073735070137</v>
       </c>
       <c r="S49" s="32" t="inlineStr">
         <is>
@@ -5727,49 +5727,49 @@
         </is>
       </c>
       <c r="T49" s="155" t="n">
-        <v>0.1943673696884233</v>
+        <v>0.2036901613035095</v>
       </c>
       <c r="U49" s="156" t="n">
-        <v>0.1938020417268023</v>
+        <v>0.2044805899965198</v>
       </c>
       <c r="V49" s="156" t="n">
-        <v>0.1941970529550974</v>
+        <v>0.205904277330852</v>
       </c>
       <c r="W49" s="156" t="n">
-        <v>0.1939036128309319</v>
+        <v>0.2065830270684989</v>
       </c>
       <c r="X49" s="157" t="n">
-        <v>0.1906912133004352</v>
+        <v>0.2039327825476363</v>
       </c>
       <c r="Y49" s="155" t="n">
-        <v>0.1934230381090656</v>
+        <v>0.193184975525806</v>
       </c>
       <c r="Z49" s="156" t="n">
-        <v>0.1932530678203309</v>
+        <v>0.1928768335092571</v>
       </c>
       <c r="AA49" s="156" t="n">
-        <v>0.1940210194145514</v>
+        <v>0.1935435435827786</v>
       </c>
       <c r="AB49" s="156" t="n">
-        <v>0.1939036128309319</v>
+        <v>0.1935197662597562</v>
       </c>
       <c r="AC49" s="157" t="n">
-        <v>0.1906912133004352</v>
+        <v>0.1905938248521335</v>
       </c>
       <c r="AD49" s="158" t="n">
-        <v>1325.507087017078</v>
+        <v>1325.646452501574</v>
       </c>
       <c r="AE49" s="159" t="n">
-        <v>1444.771731057531</v>
+        <v>1445.0231445352</v>
       </c>
       <c r="AF49" s="159" t="n">
-        <v>1586.407767486924</v>
+        <v>1586.802211748633</v>
       </c>
       <c r="AG49" s="159" t="n">
-        <v>1751.340556429061</v>
+        <v>1753.465482190792</v>
       </c>
       <c r="AH49" s="160" t="n">
-        <v>1944.259763136989</v>
+        <v>1950.073735070137</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickTop="1">
@@ -5779,49 +5779,49 @@
         </is>
       </c>
       <c r="C50" s="161" t="n">
-        <v>0.1409476775716745</v>
+        <v>0.1413112408424759</v>
       </c>
       <c r="D50" s="162" t="n">
-        <v>0.1514013908955159</v>
+        <v>0.1518511626188685</v>
       </c>
       <c r="E50" s="162" t="n">
-        <v>0.1649024135345039</v>
+        <v>0.165445585591877</v>
       </c>
       <c r="F50" s="162" t="n">
-        <v>0.1803606852372382</v>
+        <v>0.1810191935285622</v>
       </c>
       <c r="G50" s="163" t="n">
-        <v>0.1942308357103182</v>
+        <v>0.1949980890794462</v>
       </c>
       <c r="H50" s="161" t="n">
-        <v>0.1397182276551601</v>
+        <v>0.139723069253278</v>
       </c>
       <c r="I50" s="162" t="n">
-        <v>0.1504387182630833</v>
+        <v>0.1504426020307604</v>
       </c>
       <c r="J50" s="162" t="n">
-        <v>0.1642047510301971</v>
+        <v>0.1642078710604487</v>
       </c>
       <c r="K50" s="162" t="n">
-        <v>0.1799495333845529</v>
+        <v>0.1799603387699906</v>
       </c>
       <c r="L50" s="163" t="n">
-        <v>0.1941607031045022</v>
+        <v>0.1941871719678422</v>
       </c>
       <c r="M50" s="164" t="n">
-        <v>20304.91572507161</v>
+        <v>20305.05602617504</v>
       </c>
       <c r="N50" s="165" t="n">
-        <v>23755.20150315387</v>
+        <v>23755.45472960414</v>
       </c>
       <c r="O50" s="165" t="n">
-        <v>27927.72156187447</v>
+        <v>27928.11910172592</v>
       </c>
       <c r="P50" s="165" t="n">
-        <v>32939.55033653139</v>
+        <v>32941.68029351548</v>
       </c>
       <c r="Q50" s="166" t="n">
-        <v>39030.05012110031</v>
+        <v>39035.8718613594</v>
       </c>
       <c r="S50" s="42" t="inlineStr">
         <is>
@@ -5829,49 +5829,49 @@
         </is>
       </c>
       <c r="T50" s="161" t="n">
-        <v>0.1668792964919001</v>
+        <v>0.1673116076196957</v>
       </c>
       <c r="U50" s="162" t="n">
-        <v>0.179404644579044</v>
+        <v>0.1799375188339486</v>
       </c>
       <c r="V50" s="162" t="n">
-        <v>0.195489428754971</v>
+        <v>0.1961315732819088</v>
       </c>
       <c r="W50" s="162" t="n">
-        <v>0.2138747398906314</v>
+        <v>0.2146520962015944</v>
       </c>
       <c r="X50" s="163" t="n">
-        <v>0.230379857060266</v>
+        <v>0.2312852357614656</v>
       </c>
       <c r="Y50" s="161" t="n">
-        <v>0.16542583530732</v>
+        <v>0.1654148000010656</v>
       </c>
       <c r="Z50" s="162" t="n">
-        <v>0.1782639088742189</v>
+        <v>0.1782447527009876</v>
       </c>
       <c r="AA50" s="162" t="n">
-        <v>0.1946609188916174</v>
+        <v>0.19463377504809</v>
       </c>
       <c r="AB50" s="162" t="n">
-        <v>0.2133840718759099</v>
+        <v>0.2133581730326487</v>
       </c>
       <c r="AC50" s="163" t="n">
-        <v>0.2302912972942288</v>
+        <v>0.2302773864579043</v>
       </c>
       <c r="AD50" s="164" t="n">
-        <v>20304.91572507161</v>
+        <v>20305.05602617504</v>
       </c>
       <c r="AE50" s="165" t="n">
-        <v>23755.20150315387</v>
+        <v>23755.45472960414</v>
       </c>
       <c r="AF50" s="165" t="n">
-        <v>27927.72156187447</v>
+        <v>27928.11910172592</v>
       </c>
       <c r="AG50" s="165" t="n">
-        <v>32939.55033653139</v>
+        <v>32941.68029351548</v>
       </c>
       <c r="AH50" s="166" t="n">
-        <v>39030.05012110031</v>
+        <v>39035.8718613594</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -5983,49 +5983,49 @@
         </is>
       </c>
       <c r="C52" s="179" t="n">
-        <v>0.1323784544761833</v>
+        <v>0.1326991599286542</v>
       </c>
       <c r="D52" s="180" t="n">
-        <v>0.1419479697726</v>
+        <v>0.1423433496916742</v>
       </c>
       <c r="E52" s="180" t="n">
-        <v>0.154305717134623</v>
+        <v>0.1547813646175589</v>
       </c>
       <c r="F52" s="180" t="n">
-        <v>0.1682354753571241</v>
+        <v>0.1688090156736189</v>
       </c>
       <c r="G52" s="181" t="n">
-        <v>0.1807603309187224</v>
+        <v>0.1814265533312358</v>
       </c>
       <c r="H52" s="179" t="n">
-        <v>0.1312902341892914</v>
+        <v>0.1312945640172654</v>
       </c>
       <c r="I52" s="180" t="n">
-        <v>0.1410982819804833</v>
+        <v>0.1411017918328241</v>
       </c>
       <c r="J52" s="180" t="n">
-        <v>0.153691437573788</v>
+        <v>0.1536943109410401</v>
       </c>
       <c r="K52" s="180" t="n">
-        <v>0.1678743809452119</v>
+        <v>0.1678845132536353</v>
       </c>
       <c r="L52" s="181" t="n">
-        <v>0.1806963106871916</v>
+        <v>0.1807211048650451</v>
       </c>
       <c r="M52" s="182" t="n">
-        <v>20304.91572507161</v>
+        <v>20305.05602617504</v>
       </c>
       <c r="N52" s="183" t="n">
-        <v>23755.20150315387</v>
+        <v>23755.45472960414</v>
       </c>
       <c r="O52" s="183" t="n">
-        <v>27927.72156187447</v>
+        <v>27928.11910172592</v>
       </c>
       <c r="P52" s="183" t="n">
-        <v>32939.55033653139</v>
+        <v>32941.68029351548</v>
       </c>
       <c r="Q52" s="184" t="n">
-        <v>39030.05012110031</v>
+        <v>39035.8718613594</v>
       </c>
       <c r="S52" s="51" t="inlineStr">
         <is>
@@ -6033,49 +6033,49 @@
         </is>
       </c>
       <c r="T52" s="185" t="n">
-        <v>0.1481732634567613</v>
+        <v>0.1485141046061602</v>
       </c>
       <c r="U52" s="186" t="n">
-        <v>0.1587667090601117</v>
+        <v>0.1591840890121569</v>
       </c>
       <c r="V52" s="186" t="n">
-        <v>0.1723741070988326</v>
+        <v>0.1728734691095267</v>
       </c>
       <c r="W52" s="186" t="n">
-        <v>0.1874815964819093</v>
+        <v>0.1880801698159027</v>
       </c>
       <c r="X52" s="187" t="n">
-        <v>0.2011003908448568</v>
+        <v>0.2017937541612532</v>
       </c>
       <c r="Y52" s="185" t="n">
-        <v>0.1470218069747998</v>
+        <v>0.1470132034331017</v>
       </c>
       <c r="Z52" s="186" t="n">
-        <v>0.1578682248737657</v>
+        <v>0.1578533936819927</v>
       </c>
       <c r="AA52" s="186" t="n">
-        <v>0.1717250564080713</v>
+        <v>0.1717042197592525</v>
       </c>
       <c r="AB52" s="186" t="n">
-        <v>0.1870998003727495</v>
+        <v>0.1870813784718635</v>
       </c>
       <c r="AC52" s="187" t="n">
-        <v>0.2010283221128695</v>
+        <v>0.2010215312036156</v>
       </c>
       <c r="AD52" s="188" t="n">
-        <v>20304.91572507161</v>
+        <v>20305.05602617504</v>
       </c>
       <c r="AE52" s="189" t="n">
-        <v>23755.20150315387</v>
+        <v>23755.45472960414</v>
       </c>
       <c r="AF52" s="189" t="n">
-        <v>27927.72156187447</v>
+        <v>27928.11910172592</v>
       </c>
       <c r="AG52" s="189" t="n">
-        <v>32939.55033653139</v>
+        <v>32941.68029351548</v>
       </c>
       <c r="AH52" s="190" t="n">
-        <v>39030.05012110031</v>
+        <v>39035.8718613594</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,46 +6334,46 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.009347875851720144</v>
+        <v>0.00934327628064785</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.008392899637464635</v>
+        <v>0.008393112502132321</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.007637485967037326</v>
+        <v>0.007681215059739497</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.0002772129179648369</v>
+        <v>0.000277221620844592</v>
       </c>
       <c r="G57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.009265040282455884</v>
+        <v>0.009260277373332199</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.008338919126709235</v>
+        <v>0.008338919043547176</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.007604789920666475</v>
+        <v>0.007648116424786181</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>0.0002765833918750242</v>
+        <v>0.0002765834056764008</v>
       </c>
       <c r="L57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>1040.647045849234</v>
+        <v>1040.112162024087</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>1022.653522629547</v>
+        <v>1022.653608425283</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>1006.132504090373</v>
+        <v>1011.864812880436</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>39.37362695406834</v>
+        <v>39.37363346368306</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>0</v>
@@ -6384,46 +6384,46 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.01146463509339407</v>
+        <v>0.01145900830060524</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.01029341138514428</v>
+        <v>0.0102936853134754</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.009366939723198015</v>
+        <v>0.009420582725419069</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0003399857890771</v>
+        <v>0.0003399968874885021</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.01136423469490307</v>
+        <v>0.01135840963802429</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.01022798648536109</v>
+        <v>0.01022800212596628</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.009327312809029258</v>
+        <v>0.009380467763158037</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.0003392228349833469</v>
+        <v>0.0003392234003353141</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>1040.647045849234</v>
+        <v>1040.112162024087</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>1022.653522629547</v>
+        <v>1022.653608425283</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>1006.132504090373</v>
+        <v>1011.864812880436</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>39.37362695406834</v>
+        <v>39.37363346368306</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>0</v>
@@ -6538,46 +6538,46 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.007669416367819844</v>
+        <v>0.007665612450049862</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.006921504354374573</v>
+        <v>0.006921649226183484</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.006314756521830092</v>
+        <v>0.006350881350735205</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.0002295257057597091</v>
+        <v>0.0002295316784681657</v>
       </c>
       <c r="G59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.007600521529931641</v>
+        <v>0.007596614416803353</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.006875895696508608</v>
+        <v>0.006875895741173899</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.006286696035547283</v>
+        <v>0.006322513123323316</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>0.0002289687388195531</v>
+        <v>0.0002289687547949527</v>
       </c>
       <c r="L59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>1040.647045849234</v>
+        <v>1040.112162024087</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>1022.653522629547</v>
+        <v>1022.653608425283</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>1006.132504090373</v>
+        <v>1011.864812880436</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>39.37362695406834</v>
+        <v>39.37363346368306</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>0</v>
@@ -6588,46 +6588,46 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.009060555073270386</v>
+        <v>0.009056064120346485</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.008184081997933843</v>
+        <v>0.008184255301944561</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.007469905773415866</v>
+        <v>0.007512640167293703</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.0002715773454173539</v>
+        <v>0.0002715844359236447</v>
       </c>
       <c r="X59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.008979577407070621</v>
+        <v>0.008974972009554515</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.008130328848424018</v>
+        <v>0.008130338871327967</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.00743674325603302</v>
+        <v>0.007479121907328825</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.0002709155770324937</v>
+        <v>0.0002709159466440562</v>
       </c>
       <c r="AC59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>1040.647045849234</v>
+        <v>1040.112162024087</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>1022.653522629547</v>
+        <v>1022.653608425283</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>1006.132504090373</v>
+        <v>1011.864812880436</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>39.37362695406834</v>
+        <v>39.37363346368306</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>0</v>
@@ -6742,46 +6742,46 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.007223708104494291</v>
+        <v>0.007238568563490016</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.006517779514930913</v>
+        <v>0.006537072902344229</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.005940823990687222</v>
+        <v>0.005994265703932537</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.0002155905064021271</v>
+        <v>0.000216363686138018</v>
       </c>
       <c r="G61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.007160697578325963</v>
+        <v>0.007157215594890648</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.006476336778334231</v>
+        <v>0.00647643547887621</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.005915689791289215</v>
+        <v>0.005949422018678212</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>0.0002150990443298245</v>
+        <v>0.0002150980870919523</v>
       </c>
       <c r="L61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>1040.647045849234</v>
+        <v>1040.112162024087</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>1022.653522629547</v>
+        <v>1022.653608425283</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>1006.132504090373</v>
+        <v>1011.864812880436</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>39.37362695406834</v>
+        <v>39.37363346368306</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>0</v>
@@ -6792,46 +6792,46 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.008552729263153921</v>
+        <v>0.00857041899853497</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.00772331027082649</v>
+        <v>0.00774616840726316</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.007042761008651153</v>
+        <v>0.00710605096519299</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.0002556508555009883</v>
+        <v>0.0002565635050412563</v>
       </c>
       <c r="X61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.00847823793758185</v>
+        <v>0.00847325636718769</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.007674201978195347</v>
+        <v>0.007673296159023884</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.00701291286290705</v>
+        <v>0.007051784176796845</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>0.0002550643453885989</v>
+        <v>0.0002550169398347977</v>
       </c>
       <c r="AC61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>1040.647045849234</v>
+        <v>1040.112162024087</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>1022.653522629547</v>
+        <v>1022.653608425283</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>1006.132504090373</v>
+        <v>1011.864812880436</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>39.37362695406834</v>
+        <v>39.37363346368306</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>0</v>
@@ -6946,46 +6946,46 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.006784526931802449</v>
+        <v>0.006797420797768298</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.006110812880235476</v>
+        <v>0.00612776904733906</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.005559064216253906</v>
+        <v>0.005607889882439169</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.0002010968813926221</v>
+        <v>0.000201769437663038</v>
       </c>
       <c r="G63" s="181" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.006728754564060537</v>
+        <v>0.006725471363682445</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.006074234103430401</v>
+        <v>0.006074320959778791</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.005536933995878243</v>
+        <v>0.005568504796713374</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>0.0002006652544722613</v>
+        <v>0.0002006644236171125</v>
       </c>
       <c r="L63" s="181" t="n">
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>1040.647045849234</v>
+        <v>1040.112162024087</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>1022.653522629547</v>
+        <v>1022.653608425283</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>1006.132504090373</v>
+        <v>1011.864812880436</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>39.37362695406834</v>
+        <v>39.37363346368306</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>0</v>
@@ -6996,46 +6996,46 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.007594026539087004</v>
+        <v>0.007607530175433026</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.00683485401187051</v>
+        <v>0.006852749605727562</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.006210001472245061</v>
+        <v>0.006263385652121952</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.0002241023439972433</v>
+        <v>0.0002248033373566666</v>
       </c>
       <c r="X63" s="187" t="n">
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.007535013253703228</v>
+        <v>0.007530647572298024</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.006796174566525805</v>
+        <v>0.006795464220261495</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.006186618576675495</v>
+        <v>0.006221022531615468</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>0.0002236459717207249</v>
+        <v>0.0002236095292710895</v>
       </c>
       <c r="AC63" s="187" t="n">
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>1040.647045849234</v>
+        <v>1040.112162024087</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>1022.653522629547</v>
+        <v>1022.653608425283</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>1006.132504090373</v>
+        <v>1011.864812880436</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>39.37362695406834</v>
+        <v>39.37363346368306</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>0</v>
@@ -7297,49 +7297,49 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.003967630335192823</v>
+        <v>0.003965678084435026</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.005625676077348638</v>
+        <v>0.005625818758391</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.007315384306060658</v>
+        <v>0.007357269177581519</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.00891942391509444</v>
+        <v>0.008919703933335963</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.01034230280537293</v>
+        <v>0.01034265743936027</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.003932471447477667</v>
+        <v>0.003930449869204415</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.005589493484786213</v>
+        <v>0.005589493429043521</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.007284067175590782</v>
+        <v>0.007325566437211909</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.008899168689970465</v>
+        <v>0.00889916913403465</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.01033981088343212</v>
+        <v>0.01033981179647817</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>441.694225814995</v>
+        <v>441.4671986995179</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>685.4743540590321</v>
+        <v>685.4744115670497</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>963.7000921515742</v>
+        <v>969.1906478057916</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>1266.860406276849</v>
+        <v>1266.86061572601</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>1615.51274589776</v>
+        <v>1615.513091635613</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.004866071683022639</v>
+        <v>0.00486368343631152</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.00689956995615966</v>
+        <v>0.00689975356756047</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.008971900458166045</v>
+        <v>0.009023281132156351</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.01093916329783446</v>
+        <v>0.01093952039315601</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.01268424287718452</v>
+        <v>0.01268469366505001</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.00482345754553973</v>
+        <v>0.004820985147238442</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.006855716304922098</v>
+        <v>0.006855726788662193</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.008933944760799286</v>
+        <v>0.008984857969530703</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.01091461497937982</v>
+        <v>0.01091463316977979</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.0126812228651988</v>
+        <v>0.01268124496078008</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>441.694225814995</v>
+        <v>441.4671986995179</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>685.4743540590321</v>
+        <v>685.4744115670497</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>963.7000921515742</v>
+        <v>969.1906478057916</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>1266.860406276849</v>
+        <v>1266.86061572601</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>1615.51274589776</v>
+        <v>1615.513091635613</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7501,49 +7501,49 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>0.003255221776248443</v>
+        <v>0.003253607234102594</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.004639414641854586</v>
+        <v>0.004639511747968667</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.006048439362869245</v>
+        <v>0.006083040671149501</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.007385070955970965</v>
+        <v>0.00738526312998304</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.008573550906029759</v>
+        <v>0.00857379492502972</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.003225979919266236</v>
+        <v>0.003224321576684806</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.004608843617946327</v>
+        <v>0.004608843647885022</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.006021562293391194</v>
+        <v>0.00605586883914937</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.007367150347211401</v>
+        <v>0.007367150861225544</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.008570249618257569</v>
+        <v>0.008570250559421427</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>441.694225814995</v>
+        <v>441.4671986995179</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>685.4743540590321</v>
+        <v>685.4744115670497</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>963.7000921515742</v>
+        <v>969.1906478057916</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>1266.860406276849</v>
+        <v>1266.86061572601</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>1615.51274589776</v>
+        <v>1615.513091635613</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,49 +7551,49 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.003845679353537595</v>
+        <v>0.003843773204874793</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.005485707717189424</v>
+        <v>0.005485823881121952</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.007154871602833972</v>
+        <v>0.007195803725740932</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.008738097370414272</v>
+        <v>0.008738325509967958</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.01014640464862853</v>
+        <v>0.01014669352902272</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.00381130903775851</v>
+        <v>0.003809354314013739</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.005449677522579482</v>
+        <v>0.005449684240831028</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.007123107674198431</v>
+        <v>0.007163699057533123</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.00871680473801637</v>
+        <v>0.008716816630399428</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.01014225463198814</v>
+        <v>0.01014226920014176</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>441.694225814995</v>
+        <v>441.4671986995179</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>685.4743540590321</v>
+        <v>685.4744115670497</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>963.7000921515742</v>
+        <v>969.1906478057916</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>1266.860406276849</v>
+        <v>1266.86061572601</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>1615.51274589776</v>
+        <v>1615.513091635613</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,49 +7603,49 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.008847516001996398</v>
+        <v>0.009250038347826494</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>0.01264568767215641</v>
+        <v>0.01331663077455293</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>0.01638900601658188</v>
+        <v>0.0173887135037794</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>0.01978224659037122</v>
+        <v>0.02103475617778698</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.02262063825125281</v>
+        <v>0.02414430973698578</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.008807839410297301</v>
+        <v>0.008808902147082017</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.01261262944194556</v>
+        <v>0.01261757022767132</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.01637529768806599</v>
+        <v>0.01642281039171542</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.01978224659037122</v>
+        <v>0.01980365928351825</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.02262063825125281</v>
+        <v>0.02268239355257914</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>74.0718162432468</v>
+        <v>74.04515823696822</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>115.7327516516777</v>
+        <v>115.7477459605741</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>164.3606112332509</v>
+        <v>164.8239627093051</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>219.347786119544</v>
+        <v>219.6016186685324</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>283.1401131939646</v>
+        <v>283.9711710026291</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7653,49 +7653,49 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.01086161230842111</v>
+        <v>0.01137729459960519</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>0.01552442028218432</v>
+        <v>0.01637909224796429</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>0.02011988782301451</v>
+        <v>0.02138764281848815</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.02428558399958971</v>
+        <v>0.02587217575392876</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.02777012246134493</v>
+        <v>0.02969684172675346</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.01080884129278189</v>
+        <v>0.01079051813160278</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.01548044498877627</v>
+        <v>0.01544962017469306</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.02010164977544901</v>
+        <v>0.0201037114606493</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.02428558399958971</v>
+        <v>0.02423615083765559</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.02777012246134493</v>
+        <v>0.0277544129002813</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>74.0718162432468</v>
+        <v>74.04515823696822</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>115.7327516516777</v>
+        <v>115.7477459605741</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>164.3606112332509</v>
+        <v>164.8239627093051</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>219.347786119544</v>
+        <v>219.6016186685324</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>283.1401131939646</v>
+        <v>283.9711710026291</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,49 +7705,49 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.003580218050778805</v>
+        <v>0.00358766263606547</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.005106413017960178</v>
+        <v>0.005121624381491909</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.006660762933684247</v>
+        <v>0.006717878516022941</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.008137740960250075</v>
+        <v>0.008168320270345537</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.009448538508173824</v>
+        <v>0.009488600709789283</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.003548988740303681</v>
+        <v>0.003547341541747308</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.005073944333008133</v>
+        <v>0.005074116557867472</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.00663258284553814</v>
+        <v>0.006667621412879902</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.008119190092204307</v>
+        <v>0.008120540448663659</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.009445126842748466</v>
+        <v>0.009449141509357776</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>515.7660420582417</v>
+        <v>515.5123569364861</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>801.2071057107098</v>
+        <v>801.2221575276238</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>1128.060703384825</v>
+        <v>1134.014610515097</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>1486.208192396393</v>
+        <v>1486.462234394543</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>1898.652859091725</v>
+        <v>1899.484262638242</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,49 +7755,49 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.004238908223924065</v>
+        <v>0.004247769672522763</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.006050896937883297</v>
+        <v>0.006068918852588353</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.007896238223983103</v>
+        <v>0.00796387572234508</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>0.009649870363275141</v>
+        <v>0.009685973262271726</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>0.01120704106009192</v>
+        <v>0.01125433209407457</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.004201988793545415</v>
+        <v>0.004199612811252616</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.006012422604069609</v>
+        <v>0.006011825366116361</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.007862772929754023</v>
+        <v>0.00790305798254071</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.009627731784703924</v>
+        <v>0.009627586200418524</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.01120273298842752</v>
+        <v>0.01120529017954978</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>515.7660420582417</v>
+        <v>515.5123569364861</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>801.2071057107098</v>
+        <v>801.2221575276238</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>1128.060703384825</v>
+        <v>1134.014610515097</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>1486.208192396393</v>
+        <v>1486.462234394543</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>1898.652859091725</v>
+        <v>1899.484262638242</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.003362550844506271</v>
+        <v>0.00336901590471497</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.004787571345497397</v>
+        <v>0.004800945595351807</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.006232739588925477</v>
+        <v>0.006284860368592781</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.007590660442324311</v>
+        <v>0.007617347518048305</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.008793253353360626</v>
+        <v>0.008828210219085884</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.003334908913958158</v>
+        <v>0.003333355498366423</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.004758913373617465</v>
+        <v>0.004759070426987902</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.00620792751709444</v>
+        <v>0.006240720813505082</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.007574368129049555</v>
+        <v>0.007575630218849621</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.008790139030031329</v>
+        <v>0.008793883119530109</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>515.7660420582417</v>
+        <v>515.5123569364861</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>801.2071057107098</v>
+        <v>801.2221575276238</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>1128.060703384825</v>
+        <v>1134.014610515097</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>1486.208192396393</v>
+        <v>1486.462234394543</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>1898.652859091725</v>
+        <v>1899.484262638242</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,49 +7959,49 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.003763755470188112</v>
+        <v>0.003770531635329629</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.00535482788611067</v>
+        <v>0.005368948761205846</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.006962560696848668</v>
+        <v>0.007019485953442473</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.008459031218345086</v>
+        <v>0.008486940161485492</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>0.009782714366426916</v>
+        <v>0.009819277552947744</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.003734507274315509</v>
+        <v>0.003732426194977496</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.005324524126558323</v>
+        <v>0.005324067171037108</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.00693634414434078</v>
+        <v>0.006972008862639593</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.008441804859774273</v>
+        <v>0.008441870644699286</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.009779208516354622</v>
+        <v>0.009781701208797159</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>515.7660420582417</v>
+        <v>515.5123569364861</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>801.2071057107098</v>
+        <v>801.2221575276238</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>1128.060703384825</v>
+        <v>1134.014610515097</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>1486.208192396393</v>
+        <v>1486.462234394543</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>1898.652859091725</v>
+        <v>1899.484262638242</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,49 +8260,49 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>455.1559143254328</v>
+        <v>455.165925222224</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>491.6984406239189</v>
+        <v>491.7109113110098</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>527.5078579949245</v>
+        <v>516.9124224183006</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>564.0543968106415</v>
+        <v>564.0721048511863</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>596.5439566628188</v>
+        <v>596.5644119488375</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>451.1225809922559</v>
+        <v>451.1225604210558</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>488.5359897298283</v>
+        <v>488.5359848577748</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>525.2495989996962</v>
+        <v>514.6850279970544</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>562.77347901838</v>
+        <v>562.773507100503</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>596.4002226219345</v>
+        <v>596.4002752864245</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>50669977.34639457</v>
+        <v>50669979.17455942</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>59912207.23418599</v>
+        <v>59912212.26053344</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>69491820.26420976</v>
+        <v>68094108.48647761</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>80114835.79073799</v>
+        <v>80114849.03606886</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>93182764.38168105</v>
+        <v>93182784.32383816</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,49 +8310,49 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>558.2226969115127</v>
+        <v>558.2356722210162</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>603.0400154177065</v>
+        <v>603.0560635225418</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>646.9582177534894</v>
+        <v>633.9643141502561</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>691.7804573825769</v>
+        <v>691.8030396914932</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>731.6270443461442</v>
+        <v>731.653045787212</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>553.334117313464</v>
+        <v>553.3349198559583</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>599.207094426042</v>
+        <v>599.2080107316709</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>644.2212557869042</v>
+        <v>631.2647513654234</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>690.2280491676006</v>
+        <v>690.2291995081594</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>731.4528500750001</v>
+        <v>731.4541245479808</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>50669977.34639457</v>
+        <v>50669979.17455942</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>59912207.23418599</v>
+        <v>59912212.26053344</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>69491820.26420976</v>
+        <v>68094108.48647761</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>80114835.79073799</v>
+        <v>80114849.03606886</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>93182764.38168105</v>
+        <v>93182784.32383816</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8362,13 +8362,13 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>875.693094985073</v>
+        <v>875.6930949850729</v>
       </c>
       <c r="D80" s="156" t="n">
         <v>936.0944474289508</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>994.6919450383415</v>
+        <v>983.5902252041212</v>
       </c>
       <c r="F80" s="156" t="n">
         <v>1050.842000457017</v>
@@ -8377,13 +8377,13 @@
         <v>1098.57444165898</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>867.3403457868478</v>
+        <v>867.3403457868477</v>
       </c>
       <c r="I80" s="156" t="n">
         <v>929.2322263448555</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>989.5002897846119</v>
+        <v>978.4565138217483</v>
       </c>
       <c r="K80" s="156" t="n">
         <v>1047.505295581654</v>
@@ -8398,7 +8398,7 @@
         <v>24247391.29636866</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>27447814.29004065</v>
+        <v>27141470.25475444</v>
       </c>
       <c r="P80" s="159" t="n">
         <v>31009872.69463561</v>
@@ -8412,13 +8412,13 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>885.8366758565845</v>
+        <v>885.8366758565844</v>
       </c>
       <c r="U80" s="156" t="n">
         <v>946.9376866702403</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1006.213947717727</v>
+        <v>994.9836312397783</v>
       </c>
       <c r="W80" s="156" t="n">
         <v>1063.014416656095</v>
@@ -8427,13 +8427,13 @@
         <v>1111.299766040502</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>877.319243391375</v>
+        <v>877.3192433913749</v>
       </c>
       <c r="Z80" s="156" t="n">
         <v>939.9400442563862</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>1000.919747899773</v>
+        <v>989.7485197892514</v>
       </c>
       <c r="AB80" s="156" t="n">
         <v>1059.611749377654</v>
@@ -8448,7 +8448,7 @@
         <v>24247391.29636866</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>27447814.29004065</v>
+        <v>27141470.25475444</v>
       </c>
       <c r="AG80" s="159" t="n">
         <v>31009872.69463561</v>
@@ -8464,49 +8464,49 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>530.6655413687764</v>
+        <v>530.6751150720561</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>569.6074132652873</v>
+        <v>569.6193217687164</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>608.4190571685317</v>
+        <v>597.7378136437209</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>647.7934372721503</v>
+        <v>647.8102642389589</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>682.4017574423343</v>
+        <v>682.4211396398169</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>525.8985402448238</v>
+        <v>525.8985183589522</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>565.8540341876428</v>
+        <v>565.8540241860064</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>605.7154636809827</v>
+        <v>595.0678279687141</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>646.2215021051658</v>
+        <v>646.2215173787251</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>682.1389953030227</v>
+        <v>682.1390300210471</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>72004896.00180402</v>
+        <v>72004897.82996887</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>84159598.53055465</v>
+        <v>84159603.5569021</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>96939634.55425042</v>
+        <v>95235578.74123205</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>111124708.4853736</v>
+        <v>111124721.7307045</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>128584847.638309</v>
+        <v>128584867.5804661</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,49 +8514,49 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>626.921806362357</v>
+        <v>626.9333207855465</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>673.5116440182219</v>
+        <v>673.5258898472387</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>719.7162728425046</v>
+        <v>707.0812475138251</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>766.4763364558869</v>
+        <v>766.4963127226283</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>807.5912116035373</v>
+        <v>807.6141571146385</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>621.3187650079997</v>
+        <v>621.3194751200662</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>669.0880113974026</v>
+        <v>669.0888200627953</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>716.5211049069469</v>
+        <v>703.9265465641328</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>764.6086187844056</v>
+        <v>764.6096266680443</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>807.2608958825651</v>
+        <v>807.2620078524402</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>72004896.00180402</v>
+        <v>72004897.82996887</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>84159598.53055465</v>
+        <v>84159603.5569021</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>96939634.55425042</v>
+        <v>95235578.74123205</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>111124708.4853736</v>
+        <v>111124721.7307045</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>128584847.638309</v>
+        <v>128584867.5804661</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8566,49 +8566,49 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>863.5578390543295</v>
+        <v>903.1859808882475</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>915.0355100604112</v>
+        <v>963.5550509002995</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>956.1720461149794</v>
+        <v>999.7449289428605</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>993.8684570058954</v>
+        <v>1056.796091519961</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>1019.629473250404</v>
+        <v>1088.318439703112</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>859.6852230815547</v>
+        <v>860.1128586813179</v>
       </c>
       <c r="I82" s="156" t="n">
-        <v>912.6434333836097</v>
+        <v>912.9729380343285</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>955.3722709173509</v>
+        <v>944.2113934730739</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>993.8684570058954</v>
+        <v>994.9452017283575</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>1019.629473250404</v>
+        <v>1022.421739481737</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>7229746.468434094</v>
+        <v>7229867.202442009</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>8374362.880356445</v>
+        <v>8375190.927705227</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>9589173.485237585</v>
+        <v>9476372.179637089</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>11020125.78512699</v>
+        <v>11032889.10690754</v>
       </c>
       <c r="Q82" s="160" t="n">
-        <v>12762593.22417804</v>
+        <v>12800161.40916312</v>
       </c>
       <c r="S82" s="32" t="inlineStr">
         <is>
@@ -8616,49 +8616,49 @@
         </is>
       </c>
       <c r="T82" s="155" t="n">
-        <v>1060.142807494168</v>
+        <v>1110.894095397292</v>
       </c>
       <c r="U82" s="156" t="n">
-        <v>1123.339133432697</v>
+        <v>1185.146403161259</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>1173.840212632247</v>
+        <v>1229.658965004935</v>
       </c>
       <c r="W82" s="156" t="n">
-        <v>1220.118038004214</v>
+        <v>1299.830337217912</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>1251.743431058677</v>
+        <v>1338.601964779359</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>1054.992116134037</v>
+        <v>1053.600464832028</v>
       </c>
       <c r="Z82" s="156" t="n">
-        <v>1120.157103631163</v>
+        <v>1117.892341226713</v>
       </c>
       <c r="AA82" s="156" t="n">
-        <v>1172.776163278662</v>
+        <v>1155.840745857721</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>1220.118038004214</v>
+        <v>1217.63567222947</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>1251.743431058677</v>
+        <v>1251.045884995385</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>7229746.468434094</v>
+        <v>7229867.202442009</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>8374362.880356445</v>
+        <v>8375190.927705227</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>9589173.485237585</v>
+        <v>9476372.179637089</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>11020125.78512699</v>
+        <v>11032889.10690754</v>
       </c>
       <c r="AH82" s="160" t="n">
-        <v>12762593.22417804</v>
+        <v>12800161.40916312</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" thickTop="1">
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>550.0115829396108</v>
+        <v>551.4273366278021</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>589.7559092826017</v>
+        <v>591.5069311502012</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>629.0114830078668</v>
+        <v>620.311377771963</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>668.8046977612812</v>
+        <v>671.2733533982282</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>703.4075405758582</v>
+        <v>706.2685976462194</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>545.2139750160378</v>
+        <v>545.229944089755</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>586.0059974071315</v>
+        <v>586.0201549119308</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>626.3502865034192</v>
+        <v>615.670767969459</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>667.2800845108518</v>
+        <v>667.3468030104326</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>703.1535551384234</v>
+        <v>703.33151608853</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>79234642.47023812</v>
+        <v>79234765.03241089</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>92533961.4109111</v>
+        <v>92534794.48460732</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>106528808.039488</v>
+        <v>104711950.9208691</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>122144834.2705006</v>
+        <v>122157610.837612</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>141347440.8624871</v>
+        <v>141385028.9896293</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>651.2029683971482</v>
+        <v>652.8864485698632</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>698.8373664694631</v>
+        <v>700.9119174898259</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>745.6840252237789</v>
+        <v>735.3635094695262</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>793.0798809240355</v>
+        <v>795.9942237200834</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>834.3213273028758</v>
+        <v>837.6979481628335</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>645.5312148738194</v>
+        <v>645.4846908115935</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>694.3938430720161</v>
+        <v>694.3180733387881</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>742.5237184298115</v>
+        <v>729.7477580264115</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>791.260409719126</v>
+        <v>791.1959693044774</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>834.0006078507124</v>
+        <v>834.0475928305053</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>79234642.47023812</v>
+        <v>79234765.03241089</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>92533961.4109111</v>
+        <v>92534794.48460732</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>106528808.039488</v>
+        <v>104711950.9208691</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>122144834.2705006</v>
+        <v>122157610.837612</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>141347440.8624871</v>
+        <v>141385028.9896293</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8773,10 +8773,10 @@
         <v>6427.932072436402</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>6697.206360277312</v>
+        <v>6700.126495381824</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>7046.892393719899</v>
+        <v>7046.892393719898</v>
       </c>
       <c r="F84" s="156" t="n">
         <v>7326.464733788702</v>
@@ -8788,10 +8788,10 @@
         <v>6425.379721480363</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>6694.803334925235</v>
+        <v>6697.722422255749</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>7044.576352856701</v>
+        <v>7044.576352856699</v>
       </c>
       <c r="K84" s="156" t="n">
         <v>7324.311372986042</v>
@@ -8803,10 +8803,10 @@
         <v>59943029.59379703</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>69981356.14272326</v>
+        <v>70011869.6141232</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>81958614.52098854</v>
+        <v>81958614.52098852</v>
       </c>
       <c r="P84" s="159" t="n">
         <v>96436610.61872099</v>
@@ -8823,7 +8823,7 @@
         <v>3902.36696971923</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>4065.842108352229</v>
+        <v>4067.614908476834</v>
       </c>
       <c r="V84" s="156" t="n">
         <v>4278.134835048896</v>
@@ -8838,10 +8838,10 @@
         <v>3901.303136345262</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>4064.840526696178</v>
+        <v>4066.61289010828</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>4277.169517678469</v>
+        <v>4277.169517678468</v>
       </c>
       <c r="AB84" s="156" t="n">
         <v>4446.96436904227</v>
@@ -8853,10 +8853,10 @@
         <v>59943029.59379703</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>69981356.14272326</v>
+        <v>70011869.6141232</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>81958614.52098854</v>
+        <v>81958614.52098852</v>
       </c>
       <c r="AG84" s="159" t="n">
         <v>96436610.61872099</v>
@@ -8872,49 +8872,49 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>907.3726468453524</v>
+        <v>909.5654010416248</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>971.1018187164209</v>
+        <v>973.984161211898</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>1041.427129836328</v>
+        <v>1034.553195214514</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>1116.382977590383</v>
+        <v>1120.181940544438</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>1184.283010822623</v>
+        <v>1188.645308867854</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>899.9135680551136</v>
+        <v>899.9378205495501</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>965.2888904893565</v>
+        <v>965.488803386137</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>1037.281286041056</v>
+        <v>1027.287366687993</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>1113.986814391712</v>
+        <v>1114.04713245541</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>1183.863571047504</v>
+        <v>1184.023449528143</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>139177672.0640351</v>
+        <v>139177794.6262079</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>162515317.5536343</v>
+        <v>162546664.0987305</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>188487422.5604765</v>
+        <v>186670565.4418576</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>218581444.8892216</v>
+        <v>218594221.456333</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>255712218.6878394</v>
+        <v>255749806.8149815</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,49 +8922,49 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>1015.636319267229</v>
+        <v>1017.966437685571</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>1086.163050918508</v>
+        <v>1089.216895279052</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>1163.372783248337</v>
+        <v>1155.480185079009</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>1244.097075718279</v>
+        <v>1248.061359528622</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>1317.544480787878</v>
+        <v>1322.084308159043</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>1007.743795367483</v>
+        <v>1007.678748011191</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>1080.016294266431</v>
+        <v>1080.111614436737</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>1158.992265076039</v>
+        <v>1147.664963561111</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>1241.563539457442</v>
+        <v>1241.433585404709</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>1317.072309850426</v>
+        <v>1317.024964975026</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>139177672.0640351</v>
+        <v>139177794.6262079</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>162515317.5536343</v>
+        <v>162546664.0987305</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>188487422.5604765</v>
+        <v>186670565.4418576</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>218581444.8892216</v>
+        <v>218594221.456333</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>255712218.6878394</v>
+        <v>255749806.8149815</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9281,49 +9281,49 @@
         </is>
       </c>
       <c r="C90" s="74" t="n">
-        <v>111324.4401569304</v>
+        <v>111321.9957091933</v>
       </c>
       <c r="D90" s="75" t="n">
-        <v>121847.4623555101</v>
+        <v>121844.3823034031</v>
       </c>
       <c r="E90" s="75" t="n">
-        <v>131736.0854648698</v>
+        <v>131732.389343458</v>
       </c>
       <c r="F90" s="75" t="n">
-        <v>142033.88227046</v>
+        <v>142029.4468509568</v>
       </c>
       <c r="G90" s="76" t="n">
-        <v>156204.3556739109</v>
+        <v>156199.0330925568</v>
       </c>
       <c r="H90" s="74" t="n">
-        <v>995.3138995937665</v>
+        <v>997.7675215937664</v>
       </c>
       <c r="I90" s="75" t="n">
-        <v>788.7578896325715</v>
+        <v>791.8494533535065</v>
       </c>
       <c r="J90" s="75" t="n">
-        <v>566.3863438710613</v>
+        <v>570.0962203290647</v>
       </c>
       <c r="K90" s="75" t="n">
-        <v>323.2805625836594</v>
+        <v>327.732414344941</v>
       </c>
       <c r="L90" s="76" t="n">
-        <v>37.64566543256535</v>
+        <v>42.98788754186796</v>
       </c>
       <c r="M90" s="74" t="n">
-        <v>112319.7540565241</v>
+        <v>112319.7632307871</v>
       </c>
       <c r="N90" s="75" t="n">
-        <v>122636.2202451427</v>
+        <v>122636.2317567566</v>
       </c>
       <c r="O90" s="75" t="n">
-        <v>132302.4718087409</v>
+        <v>132302.485563787</v>
       </c>
       <c r="P90" s="75" t="n">
-        <v>142357.1628330436</v>
+        <v>142357.1792653017</v>
       </c>
       <c r="Q90" s="76" t="n">
-        <v>156242.0013393435</v>
+        <v>156242.0209800987</v>
       </c>
       <c r="S90" s="21" t="inlineStr">
         <is>
@@ -9331,55 +9331,55 @@
         </is>
       </c>
       <c r="T90" s="74" t="n">
-        <v>90770.18477882954</v>
+        <v>90768.07824366016</v>
       </c>
       <c r="U90" s="75" t="n">
-        <v>99350.30131074588</v>
+        <v>99347.66580502836</v>
       </c>
       <c r="V90" s="75" t="n">
-        <v>107413.1502734667</v>
+        <v>107410.0023717401</v>
       </c>
       <c r="W90" s="75" t="n">
-        <v>115809.6256344979</v>
+        <v>115805.8644434343</v>
       </c>
       <c r="X90" s="76" t="n">
-        <v>127363.7505635929</v>
+        <v>127359.2515747398</v>
       </c>
       <c r="Y90" s="74" t="n">
-        <v>801.9336952785828</v>
+        <v>803.9107205454717</v>
       </c>
       <c r="Z90" s="75" t="n">
-        <v>635.509590865103</v>
+        <v>638.0005871429162</v>
       </c>
       <c r="AA90" s="75" t="n">
-        <v>456.3427616968154</v>
+        <v>459.331911839464</v>
       </c>
       <c r="AB90" s="75" t="n">
-        <v>260.4701655128747</v>
+        <v>264.0571031429278</v>
       </c>
       <c r="AC90" s="76" t="n">
-        <v>30.33146387675285</v>
+        <v>34.63574720623246</v>
       </c>
       <c r="AD90" s="74" t="n">
-        <v>91572.11847410812</v>
+        <v>91571.98896420564</v>
       </c>
       <c r="AE90" s="75" t="n">
-        <v>99985.81090161098</v>
+        <v>99985.66639217128</v>
       </c>
       <c r="AF90" s="75" t="n">
-        <v>107869.4930351635</v>
+        <v>107869.3342835796</v>
       </c>
       <c r="AG90" s="75" t="n">
-        <v>116070.0958000108</v>
+        <v>116069.9215465772</v>
       </c>
       <c r="AH90" s="76" t="n">
-        <v>127394.0820274697</v>
+        <v>127393.8873219461</v>
       </c>
       <c r="AJ90" s="113" t="n">
-        <v>24.46098574155159</v>
+        <v>24.46095517747647</v>
       </c>
       <c r="AK90" s="114" t="n">
-        <v>24.17127990292979</v>
+        <v>24.17128348479491</v>
       </c>
       <c r="AL90" s="115" t="n">
         <v>30</v>
@@ -9388,10 +9388,10 @@
         <v>30</v>
       </c>
       <c r="AN90" s="117" t="n">
-        <v>1.226442806392686</v>
+        <v>1.226444338838569</v>
       </c>
       <c r="AO90" s="118" t="n">
-        <v>1.241142385528526</v>
+        <v>1.241142201607609</v>
       </c>
       <c r="AQ90" s="119" t="n"/>
       <c r="AR90" s="119" t="n"/>
@@ -9524,49 +9524,49 @@
         </is>
       </c>
       <c r="C92" s="85" t="n">
-        <v>135687.9058249714</v>
+        <v>135685.4613772344</v>
       </c>
       <c r="D92" s="86" t="n">
-        <v>147750.1812135974</v>
+        <v>147747.1011614904</v>
       </c>
       <c r="E92" s="86" t="n">
-        <v>159330.3717431031</v>
+        <v>159326.6756216912</v>
       </c>
       <c r="F92" s="86" t="n">
-        <v>171543.4305004977</v>
+        <v>171538.9950809944</v>
       </c>
       <c r="G92" s="87" t="n">
-        <v>188429.8307206147</v>
+        <v>188424.5081392605</v>
       </c>
       <c r="H92" s="85" t="n">
-        <v>1229.941424201886</v>
+        <v>1232.395046201886</v>
       </c>
       <c r="I92" s="86" t="n">
-        <v>980.0450387906911</v>
+        <v>983.1366025116262</v>
       </c>
       <c r="J92" s="86" t="n">
-        <v>711.1665150426037</v>
+        <v>714.8763915006072</v>
       </c>
       <c r="K92" s="86" t="n">
-        <v>417.2797565393044</v>
+        <v>421.7316083005861</v>
       </c>
       <c r="L92" s="87" t="n">
-        <v>72.58377804409656</v>
+        <v>77.92600015339917</v>
       </c>
       <c r="M92" s="85" t="n">
-        <v>136917.8472491733</v>
+        <v>136917.8564234363</v>
       </c>
       <c r="N92" s="86" t="n">
-        <v>148730.2262523881</v>
+        <v>148730.237764002</v>
       </c>
       <c r="O92" s="86" t="n">
-        <v>160041.5382581457</v>
+        <v>160041.5520131918</v>
       </c>
       <c r="P92" s="86" t="n">
-        <v>171960.710257037</v>
+        <v>171960.726689295</v>
       </c>
       <c r="Q92" s="87" t="n">
-        <v>188502.4144986588</v>
+        <v>188502.4341394139</v>
       </c>
       <c r="S92" s="42" t="inlineStr">
         <is>
@@ -9574,55 +9574,55 @@
         </is>
       </c>
       <c r="T92" s="85" t="n">
-        <v>114854.6681118086</v>
+        <v>114852.5615766392</v>
       </c>
       <c r="U92" s="86" t="n">
-        <v>124956.4120799042</v>
+        <v>124953.7765741866</v>
       </c>
       <c r="V92" s="86" t="n">
-        <v>134691.458581851</v>
+        <v>134688.3106801244</v>
       </c>
       <c r="W92" s="86" t="n">
-        <v>144981.2645217511</v>
+        <v>144977.5033306874</v>
       </c>
       <c r="X92" s="87" t="n">
-        <v>159220.2166031419</v>
+        <v>159215.7176142888</v>
       </c>
       <c r="Y92" s="85" t="n">
-        <v>1035.757313982224</v>
+        <v>1037.734339249113</v>
       </c>
       <c r="Z92" s="86" t="n">
-        <v>826.1413315458244</v>
+        <v>828.6323278236378</v>
       </c>
       <c r="AA92" s="86" t="n">
-        <v>600.6268715701337</v>
+        <v>603.6160217127822</v>
       </c>
       <c r="AB92" s="86" t="n">
-        <v>354.1472893824828</v>
+        <v>357.7342270125359</v>
       </c>
       <c r="AC92" s="87" t="n">
-        <v>65.14986779227041</v>
+        <v>69.45415112175002</v>
       </c>
       <c r="AD92" s="85" t="n">
-        <v>115890.4254257908</v>
+        <v>115890.2959158883</v>
       </c>
       <c r="AE92" s="86" t="n">
-        <v>125782.55341145</v>
+        <v>125782.4089020103</v>
       </c>
       <c r="AF92" s="86" t="n">
-        <v>135292.0854534212</v>
+        <v>135291.9267018372</v>
       </c>
       <c r="AG92" s="86" t="n">
-        <v>145335.4118111335</v>
+        <v>145335.2375576999</v>
       </c>
       <c r="AH92" s="87" t="n">
-        <v>159285.3664709342</v>
+        <v>159285.1717654105</v>
       </c>
       <c r="AJ92" s="126" t="n">
-        <v>35.47564687430621</v>
+        <v>35.47570041251289</v>
       </c>
       <c r="AK92" s="127" t="n">
-        <v>36.47680716300331</v>
+        <v>36.47680072213522</v>
       </c>
       <c r="AL92" s="128" t="n"/>
       <c r="AM92" s="129" t="n"/>
@@ -9636,49 +9636,49 @@
         </is>
       </c>
       <c r="C93" s="79" t="n">
-        <v>8372.046597771947</v>
+        <v>8004.848785774689</v>
       </c>
       <c r="D93" s="80" t="n">
-        <v>9151.95398242366</v>
+        <v>8691.969306662708</v>
       </c>
       <c r="E93" s="80" t="n">
-        <v>10028.71138536138</v>
+        <v>9478.789944608665</v>
       </c>
       <c r="F93" s="80" t="n">
-        <v>11088.11302687476</v>
+        <v>10439.94124830575</v>
       </c>
       <c r="G93" s="81" t="n">
-        <v>12516.89320385482</v>
+        <v>11761.41186457794</v>
       </c>
       <c r="H93" s="79" t="n">
-        <v>37.71347989806181</v>
+        <v>400.8704514966618</v>
       </c>
       <c r="I93" s="80" t="n">
-        <v>23.9876548361846</v>
+        <v>481.5675845154542</v>
       </c>
       <c r="J93" s="80" t="n">
-        <v>8.395381438574397</v>
+        <v>557.4924442114266</v>
       </c>
       <c r="K93" s="80" t="n">
-        <v>0</v>
+        <v>649.0002207740417</v>
       </c>
       <c r="L93" s="81" t="n">
-        <v>0</v>
+        <v>758.0416200980533</v>
       </c>
       <c r="M93" s="79" t="n">
-        <v>8409.760077670009</v>
+        <v>8405.719237271351</v>
       </c>
       <c r="N93" s="80" t="n">
-        <v>9175.941637259844</v>
+        <v>9173.536891178162</v>
       </c>
       <c r="O93" s="80" t="n">
-        <v>10037.10676679996</v>
+        <v>10036.28238882009</v>
       </c>
       <c r="P93" s="80" t="n">
-        <v>11088.11302687476</v>
+        <v>11088.94146907979</v>
       </c>
       <c r="Q93" s="81" t="n">
-        <v>12516.89320385482</v>
+        <v>12519.45348467599</v>
       </c>
       <c r="S93" s="32" t="inlineStr">
         <is>
@@ -9686,55 +9686,55 @@
         </is>
       </c>
       <c r="T93" s="79" t="n">
-        <v>6819.596772554498</v>
+        <v>6508.151616249585</v>
       </c>
       <c r="U93" s="80" t="n">
-        <v>7454.88395366953</v>
+        <v>7066.798587385697</v>
       </c>
       <c r="V93" s="80" t="n">
-        <v>8169.062008648177</v>
+        <v>7706.504363670506</v>
       </c>
       <c r="W93" s="80" t="n">
-        <v>9032.01611800852</v>
+        <v>8487.945534893228</v>
       </c>
       <c r="X93" s="81" t="n">
-        <v>10195.85396456519</v>
+        <v>9562.335739790255</v>
       </c>
       <c r="Y93" s="79" t="n">
-        <v>33.29469257523294</v>
+        <v>353.9061027498502</v>
       </c>
       <c r="Z93" s="80" t="n">
-        <v>21.17708563437581</v>
+        <v>425.149088465411</v>
       </c>
       <c r="AA93" s="80" t="n">
-        <v>7.411717104989739</v>
+        <v>492.1789009559794</v>
       </c>
       <c r="AB93" s="80" t="n">
-        <v>0</v>
+        <v>572.9659992658405</v>
       </c>
       <c r="AC93" s="81" t="n">
-        <v>0</v>
+        <v>669.2325525352885</v>
       </c>
       <c r="AD93" s="79" t="n">
-        <v>6852.891465129731</v>
+        <v>6862.057718999435</v>
       </c>
       <c r="AE93" s="80" t="n">
-        <v>7476.061039303906</v>
+        <v>7491.947675851108</v>
       </c>
       <c r="AF93" s="80" t="n">
-        <v>8176.473725753166</v>
+        <v>8198.683264626485</v>
       </c>
       <c r="AG93" s="80" t="n">
-        <v>9032.01611800852</v>
+        <v>9060.911534159068</v>
       </c>
       <c r="AH93" s="81" t="n">
-        <v>10195.85396456519</v>
+        <v>10231.56829232554</v>
       </c>
       <c r="AJ93" s="120" t="n">
-        <v>73.31107183436434</v>
+        <v>73.17235604791962</v>
       </c>
       <c r="AK93" s="121" t="n">
-        <v>79.4549413066749</v>
+        <v>79.4559667058717</v>
       </c>
       <c r="AL93" s="122" t="n">
         <v>90</v>
@@ -9743,10 +9743,10 @@
         <v>90</v>
       </c>
       <c r="AN93" s="124" t="n">
-        <v>1.227645398546919</v>
+        <v>1.229972695440614</v>
       </c>
       <c r="AO93" s="125" t="n">
-        <v>1.132717468793086</v>
+        <v>1.132702850789796</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" thickTop="1">
@@ -9756,49 +9756,49 @@
         </is>
       </c>
       <c r="C94" s="85" t="n">
-        <v>144059.9524227434</v>
+        <v>143690.3101630091</v>
       </c>
       <c r="D94" s="86" t="n">
-        <v>156902.1351960211</v>
+        <v>156439.0704681531</v>
       </c>
       <c r="E94" s="86" t="n">
-        <v>169359.0831284644</v>
+        <v>168805.4655662999</v>
       </c>
       <c r="F94" s="86" t="n">
-        <v>182631.5435273724</v>
+        <v>181978.9363293002</v>
       </c>
       <c r="G94" s="87" t="n">
-        <v>200946.7239244695</v>
+        <v>200185.9200038385</v>
       </c>
       <c r="H94" s="85" t="n">
-        <v>1267.654904099948</v>
+        <v>1633.265497698548</v>
       </c>
       <c r="I94" s="86" t="n">
-        <v>1004.032693626876</v>
+        <v>1464.70418702708</v>
       </c>
       <c r="J94" s="86" t="n">
-        <v>719.5618964811781</v>
+        <v>1272.368835712034</v>
       </c>
       <c r="K94" s="86" t="n">
-        <v>417.2797565393044</v>
+        <v>1070.731829074628</v>
       </c>
       <c r="L94" s="87" t="n">
-        <v>72.58377804409656</v>
+        <v>835.9676202514524</v>
       </c>
       <c r="M94" s="85" t="n">
-        <v>145327.6073268433</v>
+        <v>145323.5756607076</v>
       </c>
       <c r="N94" s="86" t="n">
-        <v>157906.1678896479</v>
+        <v>157903.7746551802</v>
       </c>
       <c r="O94" s="86" t="n">
-        <v>170078.6450249456</v>
+        <v>170077.8344020119</v>
       </c>
       <c r="P94" s="86" t="n">
-        <v>183048.8232839117</v>
+        <v>183049.6681583748</v>
       </c>
       <c r="Q94" s="87" t="n">
-        <v>201019.3077025136</v>
+        <v>201021.8876240899</v>
       </c>
       <c r="S94" s="42" t="inlineStr">
         <is>
@@ -9806,55 +9806,55 @@
         </is>
       </c>
       <c r="T94" s="85" t="n">
-        <v>121674.2648843631</v>
+        <v>121360.7131928888</v>
       </c>
       <c r="U94" s="86" t="n">
-        <v>132411.2960335737</v>
+        <v>132020.5751615723</v>
       </c>
       <c r="V94" s="86" t="n">
-        <v>142860.5205904992</v>
+        <v>142394.815043795</v>
       </c>
       <c r="W94" s="86" t="n">
-        <v>154013.2806397596</v>
+        <v>153465.4488655806</v>
       </c>
       <c r="X94" s="87" t="n">
-        <v>169416.0705677071</v>
+        <v>168778.053354079</v>
       </c>
       <c r="Y94" s="85" t="n">
-        <v>1069.052006557457</v>
+        <v>1391.640441998963</v>
       </c>
       <c r="Z94" s="86" t="n">
-        <v>847.3184171802002</v>
+        <v>1253.781416289049</v>
       </c>
       <c r="AA94" s="86" t="n">
-        <v>608.0385886751235</v>
+        <v>1095.794922668762</v>
       </c>
       <c r="AB94" s="86" t="n">
-        <v>354.1472893824828</v>
+        <v>930.7002262783765</v>
       </c>
       <c r="AC94" s="87" t="n">
-        <v>65.14986779227041</v>
+        <v>738.6867036570386</v>
       </c>
       <c r="AD94" s="85" t="n">
-        <v>122743.3168909205</v>
+        <v>122752.3536348877</v>
       </c>
       <c r="AE94" s="86" t="n">
-        <v>133258.6144507539</v>
+        <v>133274.3565778614</v>
       </c>
       <c r="AF94" s="86" t="n">
-        <v>143468.5591791743</v>
+        <v>143490.6099664637</v>
       </c>
       <c r="AG94" s="86" t="n">
-        <v>154367.4279291421</v>
+        <v>154396.149091859</v>
       </c>
       <c r="AH94" s="87" t="n">
-        <v>169481.2204354994</v>
+        <v>169516.7400577361</v>
       </c>
       <c r="AJ94" s="126" t="n">
-        <v>37.50672973962075</v>
+        <v>37.46110790732386</v>
       </c>
       <c r="AK94" s="127" t="n">
-        <v>38.20434753754522</v>
+        <v>38.2088332621146</v>
       </c>
       <c r="AL94" s="128" t="n"/>
       <c r="AM94" s="131" t="n"/>
@@ -9988,49 +9988,49 @@
         </is>
       </c>
       <c r="C96" s="132" t="n">
-        <v>153385.3511541392</v>
+        <v>153015.7088944049</v>
       </c>
       <c r="D96" s="133" t="n">
-        <v>167351.4706917584</v>
+        <v>166888.4059638904</v>
       </c>
       <c r="E96" s="133" t="n">
-        <v>180989.5451735538</v>
+        <v>180435.9276113893</v>
       </c>
       <c r="F96" s="133" t="n">
-        <v>195794.3190436412</v>
+        <v>195141.711845569</v>
       </c>
       <c r="G96" s="134" t="n">
-        <v>215921.5460755595</v>
+        <v>215160.7421549284</v>
       </c>
       <c r="H96" s="132" t="n">
-        <v>1271.359228419948</v>
+        <v>1636.969822018548</v>
       </c>
       <c r="I96" s="133" t="n">
-        <v>1007.783366626876</v>
+        <v>1468.45486002708</v>
       </c>
       <c r="J96" s="133" t="n">
-        <v>723.3856360511782</v>
+        <v>1276.192575282034</v>
       </c>
       <c r="K96" s="133" t="n">
-        <v>421.1496363693044</v>
+        <v>1074.601708904628</v>
       </c>
       <c r="L96" s="134" t="n">
-        <v>76.50044054409656</v>
+        <v>839.8842827514525</v>
       </c>
       <c r="M96" s="132" t="n">
-        <v>154656.7103825592</v>
+        <v>154652.6787164235</v>
       </c>
       <c r="N96" s="133" t="n">
-        <v>168359.2540583852</v>
+        <v>168356.8608239175</v>
       </c>
       <c r="O96" s="133" t="n">
-        <v>181712.930809605</v>
+        <v>181712.1201866713</v>
       </c>
       <c r="P96" s="133" t="n">
-        <v>196215.4686800106</v>
+        <v>196216.3135544736</v>
       </c>
       <c r="Q96" s="134" t="n">
-        <v>215998.0465161036</v>
+        <v>216000.6264376799</v>
       </c>
       <c r="S96" s="51" t="inlineStr">
         <is>
@@ -10038,49 +10038,49 @@
         </is>
       </c>
       <c r="T96" s="135" t="n">
-        <v>137034.9498376056</v>
+        <v>136721.3981461314</v>
       </c>
       <c r="U96" s="136" t="n">
-        <v>149623.3161459545</v>
+        <v>149232.5952739531</v>
       </c>
       <c r="V96" s="136" t="n">
-        <v>162018.0781900254</v>
+        <v>161552.3726433211</v>
       </c>
       <c r="W96" s="136" t="n">
-        <v>175694.8466123705</v>
+        <v>175147.0148381915</v>
       </c>
       <c r="X96" s="137" t="n">
-        <v>194082.4180257854</v>
+        <v>193444.4008121573</v>
       </c>
       <c r="Y96" s="135" t="n">
-        <v>1073.240660637687</v>
+        <v>1395.829096079193</v>
       </c>
       <c r="Z96" s="136" t="n">
-        <v>851.5594798971542</v>
+        <v>1258.022479006003</v>
       </c>
       <c r="AA96" s="136" t="n">
-        <v>612.3622712061436</v>
+        <v>1100.118605199782</v>
       </c>
       <c r="AB96" s="136" t="n">
-        <v>358.5231448799109</v>
+        <v>935.0760817758046</v>
       </c>
       <c r="AC96" s="137" t="n">
-        <v>69.57862265936811</v>
+        <v>743.1154585241363</v>
       </c>
       <c r="AD96" s="135" t="n">
-        <v>138108.1904982433</v>
+        <v>138117.2272422106</v>
       </c>
       <c r="AE96" s="136" t="n">
-        <v>150474.8756258516</v>
+        <v>150490.6177529591</v>
       </c>
       <c r="AF96" s="136" t="n">
-        <v>162630.4404612315</v>
+        <v>162652.4912485209</v>
       </c>
       <c r="AG96" s="136" t="n">
-        <v>176053.3697572504</v>
+        <v>176082.0909199673</v>
       </c>
       <c r="AH96" s="137" t="n">
-        <v>194151.9966484447</v>
+        <v>194187.5162706814</v>
       </c>
       <c r="AJ96" s="138" t="n"/>
       <c r="AK96" s="139" t="n"/>
